--- a/SPC26S1 - 03 March.xlsx
+++ b/SPC26S1 - 03 March.xlsx
@@ -2380,7 +2380,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="100">
+  <dxfs count="108">
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -3401,6 +3401,62 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9F9F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE4A0C8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -7140,6 +7196,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A30" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -8536,6 +8618,32 @@
     </cfRule>
     <cfRule type="expression" dxfId="60" priority="20">
       <formula>$L2=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -9011,6 +9119,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A3" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -10732,6 +10866,32 @@
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="20">
       <formula>$L2=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -12348,6 +12508,32 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AN1000">
+    <cfRule type="expression" dxfId="100" priority="21">
+      <formula>TRIM($A2)="PAID"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="22">
+      <formula>TRIM($A2)="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="23">
+      <formula>TRIM($A2)="Received"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="24">
+      <formula>TRIM($A2)="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="25">
+      <formula>TRIM($A2)="Under Review"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="26">
+      <formula>TRIM($A2)="Denied"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="27">
+      <formula>TRIM($A2)="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="28">
+      <formula>TRIM($A2)="Not found"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A13" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
@@ -12363,7 +12549,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -12538,7 +12724,127 @@
         <v>338</v>
       </c>
     </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="9"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Row colours by Claim Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="45" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each claim row is shaded by its Claim Status (column A) using conditional formatting, so the colour follows the status automatically when it is changed. Rows with no Claim Status keep their normal formatting. The deadline countdown columns keep their own colour bands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PAID - green</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Finalized - blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Received - lavender</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Pending - yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Under Review - orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Denied - red</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Rejected - pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Not found - grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Any other status is left unshaded.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A41">
+    <cfRule type="expression" dxfId="100" priority="1">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42">
+    <cfRule type="expression" dxfId="101" priority="2">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43">
+    <cfRule type="expression" dxfId="102" priority="3">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="expression" dxfId="103" priority="4">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="expression" dxfId="104" priority="5">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="expression" dxfId="105" priority="6">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47">
+    <cfRule type="expression" dxfId="106" priority="7">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="expression" dxfId="107" priority="8">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SPC26S1 - 03 March.xlsx
+++ b/SPC26S1 - 03 March.xlsx
@@ -1964,7 +1964,7 @@
     <t>2026-03 March - Specialty Claims</t>
   </si>
   <si>
-    <t>Row order - timely filing deadline</t>
+    <t>Row order - work queue, then timely filing deadline</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 0</t>
@@ -1979,7 +1979,7 @@
     <t>Past due rows sit below the claims that can still be filed on time rather than at the very top, so the actionable work stays first. That is why the numbers run up to the longest window and then restart at the negatives.</t>
   </si>
   <si>
-    <t>Filing Deadline is the date of service plus the primary payer's limit, taken from 'Carrier_Timely_Filing_Reference.xlsx'. Days Until Deadline is a live formula, so the count stays true as time passes - but the row order is a snapshot taken on 12 August 2026. Sort ascending on Days Until Deadline to bring the order up to date; that puts the past due rows first.</t>
+    <t>Filing Deadline is the date of service plus the primary payer's limit, taken from 'Carrier_Timely_Filing_Reference.xlsx'. Days Until Deadline is a live formula, so the count stays true as time passes - but the row order is a snapshot taken on 12 August 2026. Sorting on Days Until Deadline alone would mix the three groups above back together, so when you re-sort keep the empty Latest Date Worked rows first and the Finalized and PAID rows last.</t>
   </si>
   <si>
     <t>Where a payer had two possible limits the shorter one was used, so the real deadline can only be later, never earlier. Filing Limit and Limit Carrier name the figure applied and the carrier row it came from.</t>
@@ -2195,10 +2195,10 @@
     <t>66 claims with a date of service in 2026-03 March, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
-    <t>Every specialty sheet is sorted by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: claims with five days or less left sit at the top of each sheet in red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
-  </si>
-  <si>
-    <t>Order down the sheet, with the colour band each row gets, counted on 19 September 2026:</t>
+    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim goes to the bottom even when its Latest Date Worked is empty). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+  </si>
+  <si>
+    <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
   </si>
   <si>
     <t xml:space="preserve">    3 - Due in 31+ days: 23</t>
@@ -3923,67 +3923,67 @@
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C2" s="3">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="D2" s="4">
-        <v>555140726</v>
+        <v>553329086</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F2" s="6">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K2" s="3">
-        <v>46245</v>
+        <v>46266</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L30" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
-        <v>-22</v>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
+        <v>-19</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($F2="","",$F2+180-TODAY())</f>
-        <v>-22</v>
+        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <v>194</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
-        <v>6</v>
+        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <v>194</v>
       </c>
       <c r="O2" s="6">
-        <v>46278</v>
+        <v>46281</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>44</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>47</v>
@@ -4004,26 +4004,26 @@
         <v>0</v>
       </c>
       <c r="AC2" s="6">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="AD2" s="7">
         <v>1372.91</v>
       </c>
       <c r="AE2" s="4">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="5" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="AL2" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="AM2" s="6">
         <v>46119</v>
@@ -4034,58 +4034,58 @@
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>200</v>
+        <v>354</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>351</v>
+        <v>405</v>
       </c>
       <c r="C3" s="3">
-        <v>46129</v>
+        <v>46283</v>
       </c>
       <c r="D3" s="4">
-        <v>553329086</v>
+        <v>552644739</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="F3" s="6">
-        <v>46101</v>
+        <v>46093</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="K3" s="3">
-        <v>46266</v>
+        <v>46290</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-19</v>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
+        <v>158</v>
       </c>
       <c r="M3" s="12">
         <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v>194</v>
+        <v>348</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v>194</v>
+        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
+        <v>103</v>
       </c>
       <c r="O3" s="6">
-        <v>46281</v>
+        <v>46458</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>57</v>
@@ -4094,7 +4094,7 @@
         <v>47</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>47</v>
@@ -4106,7 +4106,7 @@
         <v>48</v>
       </c>
       <c r="Z3" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
@@ -4114,27 +4114,25 @@
       <c r="AB3" s="7">
         <v>0</v>
       </c>
-      <c r="AC3" s="6">
-        <v>46129</v>
-      </c>
+      <c r="AC3" s="6"/>
       <c r="AD3" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AE3" s="4">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="AG3" s="5"/>
       <c r="AH3" s="5"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="5" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="AM3" s="6">
         <v>46119</v>
@@ -4145,52 +4143,52 @@
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>354</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C4" s="3">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="D4" s="4">
-        <v>551389428</v>
+        <v>554160609</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="F4" s="6">
-        <v>46083</v>
+        <v>46108</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>64</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="K4" s="3">
         <v>46268</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>148</v>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
+        <v>173</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" ref="M4:M11" ca="1" si="1">IF($C4="","",$C4+365-TODAY())</f>
-        <v>206</v>
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <v>199</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" ref="N4:N11" ca="1" si="2">IF($C4="","",$C4+120-TODAY())</f>
-        <v>-39</v>
+        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <v>-46</v>
       </c>
       <c r="O4" s="6">
-        <v>46448</v>
+        <v>46473</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>57</v>
@@ -4217,37 +4215,37 @@
         <v>48</v>
       </c>
       <c r="Z4" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA4" s="7">
-        <v>1184.69</v>
+        <v>1184.44</v>
       </c>
       <c r="AB4" s="7">
-        <v>198.17</v>
+        <v>148.02000000000001</v>
       </c>
       <c r="AC4" s="6">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="AD4" s="7">
-        <v>43.39</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="AE4" s="4">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="AG4" s="5"/>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="4">
-        <v>559119307</v>
+        <v>559120425</v>
       </c>
       <c r="AK4" s="5" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AM4" s="6">
         <v>46119</v>
@@ -4258,25 +4256,25 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>386</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="C5" s="3">
-        <v>46141</v>
+        <v>46268</v>
       </c>
       <c r="D5" s="4">
-        <v>552404210</v>
+        <v>555138984</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F5" s="6">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>64</v>
@@ -4285,25 +4283,25 @@
         <v>70</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K5" s="3">
-        <v>46268</v>
+        <v>46254</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>157</v>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
+        <v>173</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>206</v>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <v>333</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-39</v>
+        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <v>88</v>
       </c>
       <c r="O5" s="6">
-        <v>46457</v>
+        <v>46473</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>57</v>
@@ -4333,31 +4331,27 @@
         <v>1372.91</v>
       </c>
       <c r="AA5" s="7">
-        <v>1147.73</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="7">
-        <v>184.73</v>
-      </c>
-      <c r="AC5" s="6">
-        <v>46141</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC5" s="6"/>
       <c r="AD5" s="7">
-        <v>40.450000000000003</v>
+        <v>1372.91</v>
       </c>
       <c r="AE5" s="4">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
-      <c r="AJ5" s="4">
-        <v>559120113</v>
-      </c>
+      <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="AL5" s="5" t="s">
         <v>73</v>
@@ -4371,22 +4365,22 @@
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>354</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>405</v>
+        <v>356</v>
       </c>
       <c r="C6" s="3">
-        <v>46283</v>
+        <v>46125</v>
       </c>
       <c r="D6" s="4">
-        <v>552644739</v>
+        <v>554403926</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F6" s="6">
-        <v>46093</v>
+        <v>46111</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>64</v>
@@ -4395,28 +4389,28 @@
         <v>64</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>78</v>
       </c>
       <c r="K6" s="3">
-        <v>46290</v>
+        <v>46268</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>158</v>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
+        <v>176</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>348</v>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <v>190</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>103</v>
+        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <v>-55</v>
       </c>
       <c r="O6" s="6">
-        <v>46458</v>
+        <v>46476</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>57</v>
@@ -4451,12 +4445,14 @@
       <c r="AB6" s="7">
         <v>0</v>
       </c>
-      <c r="AC6" s="6"/>
+      <c r="AC6" s="6">
+        <v>46125</v>
+      </c>
       <c r="AD6" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE6" s="4">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="AF6" s="5" t="s">
         <v>79</v>
@@ -4466,10 +4462,10 @@
       <c r="AI6" s="5"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="AM6" s="6">
         <v>46119</v>
@@ -4480,67 +4476,67 @@
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C7" s="3">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="D7" s="4">
-        <v>552606577</v>
+        <v>566722180</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F7" s="6">
-        <v>46094</v>
+        <v>46085</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="J7" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K7" s="3">
-        <v>46268</v>
+        <v>46231</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>159</v>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
+        <v>-125</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>206</v>
+        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
+        <v>-125</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-39</v>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <v>199</v>
       </c>
       <c r="O7" s="6">
-        <v>46459</v>
+        <v>46175</v>
       </c>
       <c r="P7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T7" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T7" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>47</v>
@@ -4549,37 +4545,35 @@
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="Z7" s="7">
-        <v>1426.25</v>
+        <v>1769.18</v>
       </c>
       <c r="AA7" s="7">
-        <v>1184.69</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="7">
-        <v>198.17</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="6">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="AD7" s="7">
-        <v>43.39</v>
+        <v>1769.18</v>
       </c>
       <c r="AE7" s="4">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
-      <c r="AJ7" s="4">
-        <v>559120100</v>
-      </c>
+      <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="AL7" s="5" t="s">
         <v>60</v>
@@ -4593,58 +4587,58 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C8" s="3">
-        <v>46210</v>
+        <v>46141</v>
       </c>
       <c r="D8" s="4">
-        <v>552857208</v>
+        <v>551769931</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F8" s="6">
-        <v>46094</v>
+        <v>46086</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="K8" s="3">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>159</v>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
+        <v>-124</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>275</v>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v>206</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v>206</v>
       </c>
       <c r="O8" s="6">
-        <v>46459</v>
+        <v>46176</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="R8" s="5" t="s">
         <v>57</v>
@@ -4653,7 +4647,7 @@
         <v>47</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>47</v>
@@ -4665,34 +4659,32 @@
         <v>48</v>
       </c>
       <c r="Z8" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA8" s="7">
-        <v>1223.6600000000001</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="7">
-        <v>159.19999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="6">
-        <v>46210</v>
+        <v>46141</v>
       </c>
       <c r="AD8" s="7">
-        <v>43.39</v>
+        <v>1372.91</v>
       </c>
       <c r="AE8" s="4">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="AG8" s="5"/>
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
-      <c r="AJ8" s="4">
-        <v>559120090</v>
-      </c>
+      <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AL8" s="5" t="s">
         <v>73</v>
@@ -4709,64 +4701,64 @@
         <v>354</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C9" s="3">
-        <v>46134</v>
+        <v>46196</v>
       </c>
       <c r="D9" s="4">
-        <v>554160609</v>
+        <v>551830492</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="F9" s="6">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="K9" s="3">
         <v>46268</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>173</v>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
+        <v>-123</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>199</v>
+        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
+        <v>76</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-46</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>261</v>
       </c>
       <c r="O9" s="6">
-        <v>46473</v>
+        <v>46177</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="S9" s="5" t="s">
         <v>47</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>47</v>
@@ -4778,37 +4770,37 @@
         <v>48</v>
       </c>
       <c r="Z9" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA9" s="7">
-        <v>1184.44</v>
+        <v>1223.69</v>
       </c>
       <c r="AB9" s="7">
-        <v>148.02000000000001</v>
+        <v>354.8</v>
       </c>
       <c r="AC9" s="6">
-        <v>46134</v>
+        <v>46196</v>
       </c>
       <c r="AD9" s="7">
-        <v>40.450000000000003</v>
+        <v>-152.24</v>
       </c>
       <c r="AE9" s="4">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4">
-        <v>559120425</v>
+        <v>560056768</v>
       </c>
       <c r="AK9" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="AM9" s="6">
         <v>46119</v>
@@ -4819,58 +4811,58 @@
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>387</v>
+        <v>344</v>
       </c>
       <c r="C10" s="3">
-        <v>46268</v>
+        <v>46121</v>
       </c>
       <c r="D10" s="4">
-        <v>555138984</v>
+        <v>551874008</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="F10" s="6">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K10" s="3">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>173</v>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
+        <v>-123</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>333</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>186</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>88</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>186</v>
       </c>
       <c r="O10" s="6">
-        <v>46473</v>
+        <v>46177</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="R10" s="5" t="s">
         <v>57</v>
@@ -4879,7 +4871,7 @@
         <v>47</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="U10" s="5" t="s">
         <v>47</v>
@@ -4891,7 +4883,7 @@
         <v>48</v>
       </c>
       <c r="Z10" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -4899,12 +4891,14 @@
       <c r="AB10" s="7">
         <v>0</v>
       </c>
-      <c r="AC10" s="6"/>
+      <c r="AC10" s="6">
+        <v>46121</v>
+      </c>
       <c r="AD10" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AE10" s="4">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="AF10" s="5" t="s">
         <v>68</v>
@@ -4914,7 +4908,7 @@
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AL10" s="5" t="s">
         <v>73</v>
@@ -4931,55 +4925,55 @@
         <v>200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="C11" s="3">
-        <v>46125</v>
+        <v>46121</v>
       </c>
       <c r="D11" s="4">
-        <v>554403926</v>
+        <v>552405449</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F11" s="6">
-        <v>46111</v>
+        <v>46092</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>78</v>
       </c>
       <c r="K11" s="3">
-        <v>46268</v>
+        <v>46257</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>176</v>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
+        <v>-118</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>190</v>
+        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <v>186</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-55</v>
+        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <v>186</v>
       </c>
       <c r="O11" s="6">
-        <v>46476</v>
+        <v>46182</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="R11" s="5" t="s">
         <v>57</v>
@@ -4988,7 +4982,7 @@
         <v>47</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="U11" s="5" t="s">
         <v>47</v>
@@ -5009,13 +5003,13 @@
         <v>0</v>
       </c>
       <c r="AC11" s="6">
-        <v>46125</v>
+        <v>46121</v>
       </c>
       <c r="AD11" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE11" s="4">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="AF11" s="5" t="s">
         <v>79</v>
@@ -5025,10 +5019,10 @@
       <c r="AI11" s="5"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AM11" s="6">
         <v>46119</v>
@@ -5042,19 +5036,19 @@
         <v>200</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C12" s="3">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="D12" s="4">
-        <v>566722180</v>
+        <v>552859864</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="F12" s="6">
-        <v>46085</v>
+        <v>46097</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>70</v>
@@ -5063,28 +5057,28 @@
         <v>70</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K12" s="3">
-        <v>46231</v>
+        <v>46268</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-125</v>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
+        <v>-113</v>
       </c>
       <c r="M12" s="12">
         <f ca="1">IF($F12="","",$F12+90-TODAY())</f>
-        <v>-125</v>
+        <v>-113</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" ref="N12:N23" ca="1" si="3">IF($C12="","",$C12+365-TODAY())</f>
-        <v>199</v>
+        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <v>200</v>
       </c>
       <c r="O12" s="6">
-        <v>46175</v>
+        <v>46187</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>97</v>
@@ -5108,10 +5102,10 @@
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="Z12" s="7">
-        <v>1769.18</v>
+        <v>1426.25</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -5120,26 +5114,28 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="AD12" s="7">
-        <v>1769.18</v>
+        <v>1426.25</v>
       </c>
       <c r="AE12" s="4">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG12" s="5"/>
+        <v>79</v>
+      </c>
+      <c r="AG12" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="AM12" s="6">
         <v>46119</v>
@@ -5153,58 +5149,58 @@
         <v>200</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="C13" s="3">
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="D13" s="4">
-        <v>551769931</v>
+        <v>553133483</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F13" s="6">
-        <v>46086</v>
+        <v>46099</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="K13" s="3">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-124</v>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
+        <v>-111</v>
       </c>
       <c r="M13" s="12">
+        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <v>41</v>
+      </c>
+      <c r="N13" s="12">
         <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v>206</v>
-      </c>
-      <c r="N13" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="O13" s="6">
-        <v>46176</v>
+        <v>46189</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>97</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="S13" s="5" t="s">
         <v>47</v>
@@ -5222,7 +5218,7 @@
         <v>48</v>
       </c>
       <c r="Z13" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -5231,26 +5227,26 @@
         <v>0</v>
       </c>
       <c r="AC13" s="6">
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="AD13" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AE13" s="4">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AG13" s="5"/>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="AM13" s="6">
         <v>46119</v>
@@ -5261,61 +5257,61 @@
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>354</v>
+        <v>200</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C14" s="3">
-        <v>46196</v>
+        <v>46167</v>
       </c>
       <c r="D14" s="4">
-        <v>551830492</v>
+        <v>553148506</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F14" s="6">
-        <v>46087</v>
+        <v>46099</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="K14" s="3">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-123</v>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
+        <v>-111</v>
       </c>
       <c r="M14" s="12">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
-        <v>76</v>
+        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <v>232</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>261</v>
+        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <v>232</v>
       </c>
       <c r="O14" s="6">
-        <v>46177</v>
+        <v>46189</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>97</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="S14" s="5" t="s">
         <v>47</v>
@@ -5333,40 +5329,40 @@
         <v>48</v>
       </c>
       <c r="Z14" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA14" s="7">
-        <v>1223.69</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="7">
-        <v>354.8</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="6">
-        <v>46196</v>
+        <v>46167</v>
       </c>
       <c r="AD14" s="7">
-        <v>-152.24</v>
+        <v>1372.91</v>
       </c>
       <c r="AE14" s="4">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AG14" s="5"/>
+        <v>116</v>
+      </c>
+      <c r="AG14" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
-      <c r="AJ14" s="4">
-        <v>560056768</v>
-      </c>
+      <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="AL14" s="5" t="s">
         <v>60</v>
       </c>
       <c r="AM14" s="6">
-        <v>46119</v>
+        <v>46153</v>
       </c>
       <c r="AN14" s="5" t="s">
         <v>52</v>
@@ -5374,28 +5370,28 @@
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>200</v>
+        <v>386</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="C15" s="3">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="D15" s="4">
-        <v>551874008</v>
+        <v>553498942</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F15" s="6">
-        <v>46087</v>
+        <v>46101</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>42</v>
@@ -5404,34 +5400,34 @@
         <v>65</v>
       </c>
       <c r="K15" s="3">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-123</v>
+        <f ca="1">IF($O15="","",$O15-TODAY())</f>
+        <v>-109</v>
       </c>
       <c r="M15" s="12">
+        <f ca="1">IF($F15="","",$F15+90-TODAY())</f>
+        <v>-109</v>
+      </c>
+      <c r="N15" s="12">
         <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
-        <v>186</v>
-      </c>
-      <c r="N15" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="O15" s="6">
-        <v>46177</v>
+        <v>46191</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>97</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T15" s="5" t="s">
         <v>57</v>
@@ -5455,13 +5451,13 @@
         <v>0</v>
       </c>
       <c r="AC15" s="6">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="AD15" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE15" s="4">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="AF15" s="5" t="s">
         <v>68</v>
@@ -5471,7 +5467,7 @@
       <c r="AI15" s="5"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AL15" s="5" t="s">
         <v>73</v>
@@ -5488,19 +5484,19 @@
         <v>200</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C16" s="3">
-        <v>46121</v>
+        <v>46141</v>
       </c>
       <c r="D16" s="4">
-        <v>552405449</v>
+        <v>554088972</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F16" s="6">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>101</v>
@@ -5512,25 +5508,25 @@
         <v>42</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="K16" s="3">
-        <v>46257</v>
+        <v>46266</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-118</v>
+        <f ca="1">IF($O16="","",$O16-TODAY())</f>
+        <v>-102</v>
       </c>
       <c r="M16" s="12">
         <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>186</v>
+        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <v>206</v>
       </c>
       <c r="O16" s="6">
-        <v>46182</v>
+        <v>46198</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>97</v>
@@ -5557,7 +5553,7 @@
         <v>48</v>
       </c>
       <c r="Z16" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA16" s="7">
         <v>0</v>
@@ -5566,13 +5562,13 @@
         <v>0</v>
       </c>
       <c r="AC16" s="6">
-        <v>46121</v>
+        <v>46141</v>
       </c>
       <c r="AD16" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AE16" s="4">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="AF16" s="5" t="s">
         <v>79</v>
@@ -5582,10 +5578,10 @@
       <c r="AI16" s="5"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AL16" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="AM16" s="6">
         <v>46119</v>
@@ -5596,22 +5592,22 @@
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>406</v>
+        <v>361</v>
       </c>
       <c r="C17" s="3">
-        <v>46288</v>
+        <v>46197</v>
       </c>
       <c r="D17" s="4">
-        <v>563362999</v>
+        <v>563362114</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="F17" s="6">
-        <v>46094</v>
+        <v>46108</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>104</v>
@@ -5623,25 +5619,25 @@
         <v>42</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="K17" s="3">
-        <v>46286</v>
+        <v>46148</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-116</v>
+        <f ca="1">IF($O17="","",$O17-TODAY())</f>
+        <v>-102</v>
       </c>
       <c r="M17" s="12">
         <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>353</v>
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <v>262</v>
       </c>
       <c r="O17" s="6">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>97</v>
@@ -5679,23 +5675,23 @@
         <v>0</v>
       </c>
       <c r="AC17" s="6">
-        <v>46223</v>
+        <v>46197</v>
       </c>
       <c r="AD17" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE17" s="4">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="AF17" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AG17" s="5"/>
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AL17" s="5" t="s">
         <v>60</v>
@@ -5709,67 +5705,67 @@
     </row>
     <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>200</v>
+        <v>354</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>359</v>
+        <v>407</v>
       </c>
       <c r="C18" s="3">
-        <v>46135</v>
+        <v>46184</v>
       </c>
       <c r="D18" s="4">
-        <v>552859864</v>
+        <v>553283455</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="F18" s="6">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="K18" s="3">
-        <v>46268</v>
+        <v>46300</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-113</v>
+        <f ca="1">IF($O18="","",$O18-TODAY())</f>
+        <v>-80</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($F18="","",$F18+90-TODAY())</f>
-        <v>-113</v>
+        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
+        <v>64</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>200</v>
+        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
+        <v>64</v>
       </c>
       <c r="O18" s="6">
-        <v>46187</v>
+        <v>46220</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="U18" s="5" t="s">
         <v>47</v>
@@ -5790,28 +5786,26 @@
         <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <v>46135</v>
+        <v>46184</v>
       </c>
       <c r="AD18" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE18" s="4">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG18" s="5" t="s">
-        <v>58</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="AG18" s="5"/>
       <c r="AH18" s="5"/>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="AL18" s="5" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AM18" s="6">
         <v>46119</v>
@@ -5825,64 +5819,64 @@
         <v>200</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C19" s="3">
-        <v>46161</v>
+        <v>46128</v>
       </c>
       <c r="D19" s="4">
-        <v>553133483</v>
+        <v>554404221</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="F19" s="6">
-        <v>46099</v>
+        <v>46112</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="K19" s="3">
         <v>46268</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-111</v>
+        <f ca="1">IF($O19="","",$O19-TODAY())</f>
+        <v>-68</v>
       </c>
       <c r="M19" s="12">
-        <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
-        <v>41</v>
+        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <v>193</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>226</v>
+        <f ca="1">IF($C19="","",$C19+90-TODAY())</f>
+        <v>-82</v>
       </c>
       <c r="O19" s="6">
-        <v>46189</v>
+        <v>46232</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="S19" s="5" t="s">
         <v>47</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="U19" s="5" t="s">
         <v>47</v>
@@ -5894,7 +5888,7 @@
         <v>48</v>
       </c>
       <c r="Z19" s="7">
-        <v>1426.25</v>
+        <v>976.64</v>
       </c>
       <c r="AA19" s="7">
         <v>0</v>
@@ -5903,26 +5897,26 @@
         <v>0</v>
       </c>
       <c r="AC19" s="6">
-        <v>46161</v>
+        <v>46128</v>
       </c>
       <c r="AD19" s="7">
-        <v>1426.25</v>
+        <v>976.64</v>
       </c>
       <c r="AE19" s="4">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="AG19" s="5"/>
       <c r="AH19" s="5"/>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AL19" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="AM19" s="6">
         <v>46119</v>
@@ -5936,25 +5930,25 @@
         <v>200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="C20" s="3">
-        <v>46167</v>
+        <v>46128</v>
       </c>
       <c r="D20" s="4">
-        <v>553148506</v>
+        <v>553124954</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="F20" s="6">
         <v>46099</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>42</v>
@@ -5963,41 +5957,23 @@
         <v>43</v>
       </c>
       <c r="K20" s="3">
-        <v>46265</v>
-      </c>
-      <c r="L20" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-111</v>
-      </c>
-      <c r="M20" s="12">
-        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
-        <v>232</v>
-      </c>
-      <c r="N20" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>232</v>
-      </c>
-      <c r="O20" s="6">
-        <v>46189</v>
-      </c>
-      <c r="P20" s="5" t="s">
-        <v>97</v>
-      </c>
+        <v>46269</v>
+      </c>
+      <c r="L20" s="12" t="str">
+        <f ca="1">IF($O20="","",$O20-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="5"/>
       <c r="Q20" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="R20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="S20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="U20" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
       <c r="V20" s="5"/>
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
@@ -6014,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="AC20" s="6">
-        <v>46167</v>
+        <v>46128</v>
       </c>
       <c r="AD20" s="7">
         <v>1372.91</v>
@@ -6023,22 +5999,20 @@
         <v>143</v>
       </c>
       <c r="AF20" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG20" s="5" t="s">
-        <v>58</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="AG20" s="5"/>
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="AL20" s="5" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="AM20" s="6">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="AN20" s="5" t="s">
         <v>52</v>
@@ -6046,67 +6020,67 @@
     </row>
     <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>342</v>
+        <v>61</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C21" s="3">
-        <v>46185</v>
+        <v>46126</v>
       </c>
       <c r="D21" s="4">
-        <v>553362911</v>
+        <v>555140726</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="F21" s="6">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="K21" s="3">
-        <v>46266</v>
+        <v>46245</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-109</v>
+        <f ca="1">IF($O21="","",$O21-TODAY())</f>
+        <v>-22</v>
       </c>
       <c r="M21" s="12">
-        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>250</v>
+        <f ca="1">IF($F21="","",$F21+180-TODAY())</f>
+        <v>-22</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>250</v>
+        <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
+        <v>6</v>
       </c>
       <c r="O21" s="6">
-        <v>46191</v>
+        <v>46278</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T21" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="U21" s="5" t="s">
         <v>47</v>
@@ -6118,35 +6092,35 @@
         <v>48</v>
       </c>
       <c r="Z21" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA21" s="7">
-        <v>1245.54</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="7">
-        <v>361.42</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="6">
-        <v>46185</v>
+        <v>46126</v>
       </c>
       <c r="AD21" s="7">
-        <v>-180.71</v>
+        <v>1372.91</v>
       </c>
       <c r="AE21" s="4">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="AG21" s="5"/>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="AL21" s="5" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="AM21" s="6">
         <v>46119</v>
@@ -6157,31 +6131,31 @@
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>386</v>
+        <v>61</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>388</v>
+        <v>352</v>
       </c>
       <c r="C22" s="3">
-        <v>46124</v>
+        <v>46141</v>
       </c>
       <c r="D22" s="4">
-        <v>553498942</v>
+        <v>551389428</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="F22" s="6">
-        <v>46101</v>
+        <v>46083</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>65</v>
@@ -6190,34 +6164,34 @@
         <v>46268</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-109</v>
+        <f ca="1">IF($O22="","",$O22-TODAY())</f>
+        <v>148</v>
       </c>
       <c r="M22" s="12">
-        <f ca="1">IF($F22="","",$F22+90-TODAY())</f>
-        <v>-109</v>
+        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
+        <v>206</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>189</v>
+        <f ca="1">IF($C22="","",$C22+120-TODAY())</f>
+        <v>-39</v>
       </c>
       <c r="O22" s="6">
-        <v>46191</v>
+        <v>46448</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T22" s="5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="U22" s="5" t="s">
         <v>47</v>
@@ -6232,19 +6206,19 @@
         <v>1426.25</v>
       </c>
       <c r="AA22" s="7">
-        <v>0</v>
+        <v>1184.69</v>
       </c>
       <c r="AB22" s="7">
-        <v>0</v>
+        <v>198.17</v>
       </c>
       <c r="AC22" s="6">
-        <v>46124</v>
+        <v>46141</v>
       </c>
       <c r="AD22" s="7">
-        <v>1426.25</v>
+        <v>43.39</v>
       </c>
       <c r="AE22" s="4">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="AF22" s="5" t="s">
         <v>68</v>
@@ -6252,12 +6226,14 @@
       <c r="AG22" s="5"/>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
-      <c r="AJ22" s="4"/>
+      <c r="AJ22" s="4">
+        <v>559119307</v>
+      </c>
       <c r="AK22" s="5" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="AL22" s="5" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="AM22" s="6">
         <v>46119</v>
@@ -6271,55 +6247,55 @@
         <v>61</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C23" s="3">
         <v>46141</v>
       </c>
       <c r="D23" s="4">
-        <v>555169750</v>
+        <v>552404210</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="F23" s="6">
-        <v>46104</v>
+        <v>46092</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="K23" s="3">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-106</v>
+        <f ca="1">IF($O23="","",$O23-TODAY())</f>
+        <v>157</v>
       </c>
       <c r="M23" s="12">
         <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
         <v>206</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>206</v>
+        <f ca="1">IF($C23="","",$C23+120-TODAY())</f>
+        <v>-39</v>
       </c>
       <c r="O23" s="6">
-        <v>46194</v>
+        <v>46457</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="R23" s="5" t="s">
         <v>57</v>
@@ -6328,7 +6304,7 @@
         <v>47</v>
       </c>
       <c r="T23" s="5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="U23" s="5" t="s">
         <v>47</v>
@@ -6340,40 +6316,40 @@
         <v>48</v>
       </c>
       <c r="Z23" s="7">
-        <v>396.27</v>
+        <v>1372.91</v>
       </c>
       <c r="AA23" s="7">
-        <v>0</v>
+        <v>1147.73</v>
       </c>
       <c r="AB23" s="7">
-        <v>0</v>
+        <v>184.73</v>
       </c>
       <c r="AC23" s="6">
         <v>46141</v>
       </c>
       <c r="AD23" s="7">
-        <v>396.27</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="AE23" s="4">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="AF23" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="AG23" s="5" t="s">
-        <v>122</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AG23" s="5"/>
       <c r="AH23" s="5"/>
       <c r="AI23" s="5"/>
-      <c r="AJ23" s="4"/>
+      <c r="AJ23" s="4">
+        <v>559120113</v>
+      </c>
       <c r="AK23" s="5" t="s">
         <v>69</v>
       </c>
       <c r="AL23" s="5" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="AM23" s="6">
-        <v>46105</v>
+        <v>46119</v>
       </c>
       <c r="AN23" s="5" t="s">
         <v>52</v>
@@ -6384,64 +6360,64 @@
         <v>61</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C24" s="3">
-        <v>46123</v>
+        <v>46141</v>
       </c>
       <c r="D24" s="4">
-        <v>554246495</v>
+        <v>552606577</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="F24" s="6">
-        <v>46106</v>
+        <v>46094</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="K24" s="3">
         <v>46268</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-104</v>
+        <f ca="1">IF($O24="","",$O24-TODAY())</f>
+        <v>159</v>
       </c>
       <c r="M24" s="12">
-        <f ca="1">IF($F24="","",$F24+90-TODAY())</f>
-        <v>-104</v>
+        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
+        <v>206</v>
       </c>
       <c r="N24" s="12">
-        <f ca="1">IF($C24="","",$C24+540-TODAY())</f>
-        <v>363</v>
+        <f ca="1">IF($C24="","",$C24+120-TODAY())</f>
+        <v>-39</v>
       </c>
       <c r="O24" s="6">
-        <v>46196</v>
+        <v>46459</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="R24" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T24" s="5" t="s">
-        <v>393</v>
+        <v>67</v>
       </c>
       <c r="U24" s="5" t="s">
         <v>47</v>
@@ -6453,37 +6429,37 @@
         <v>48</v>
       </c>
       <c r="Z24" s="7">
-        <v>1029.98</v>
+        <v>1426.25</v>
       </c>
       <c r="AA24" s="7">
-        <v>883.53</v>
+        <v>1184.69</v>
       </c>
       <c r="AB24" s="7">
-        <v>121.45</v>
+        <v>198.17</v>
       </c>
       <c r="AC24" s="6">
-        <v>46123</v>
+        <v>46141</v>
       </c>
       <c r="AD24" s="7">
-        <v>25</v>
+        <v>43.39</v>
       </c>
       <c r="AE24" s="4">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="AF24" s="5" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="AG24" s="5"/>
       <c r="AH24" s="5"/>
       <c r="AI24" s="5"/>
       <c r="AJ24" s="4">
-        <v>557570817</v>
+        <v>559120100</v>
       </c>
       <c r="AK24" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AL24" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="AM24" s="6">
         <v>46119</v>
@@ -6494,58 +6470,58 @@
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C25" s="3">
-        <v>46141</v>
+        <v>46210</v>
       </c>
       <c r="D25" s="4">
-        <v>554088972</v>
+        <v>552857208</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="F25" s="6">
-        <v>46108</v>
+        <v>46094</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="K25" s="3">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-102</v>
+        <f ca="1">IF($O25="","",$O25-TODAY())</f>
+        <v>159</v>
       </c>
       <c r="M25" s="12">
         <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="N25" s="12">
-        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
-        <v>206</v>
+        <f ca="1">IF($C25="","",$C25+120-TODAY())</f>
+        <v>30</v>
       </c>
       <c r="O25" s="6">
-        <v>46198</v>
+        <v>46459</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="R25" s="5" t="s">
         <v>57</v>
@@ -6554,7 +6530,7 @@
         <v>47</v>
       </c>
       <c r="T25" s="5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="U25" s="5" t="s">
         <v>47</v>
@@ -6566,35 +6542,37 @@
         <v>48</v>
       </c>
       <c r="Z25" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA25" s="7">
-        <v>0</v>
+        <v>1223.6600000000001</v>
       </c>
       <c r="AB25" s="7">
-        <v>0</v>
+        <v>159.19999999999999</v>
       </c>
       <c r="AC25" s="6">
-        <v>46141</v>
+        <v>46210</v>
       </c>
       <c r="AD25" s="7">
-        <v>1372.91</v>
+        <v>43.39</v>
       </c>
       <c r="AE25" s="4">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="AF25" s="5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="AG25" s="5"/>
       <c r="AH25" s="5"/>
       <c r="AI25" s="5"/>
-      <c r="AJ25" s="4"/>
+      <c r="AJ25" s="4">
+        <v>559120090</v>
+      </c>
       <c r="AK25" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AL25" s="5" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="AM25" s="6">
         <v>46119</v>
@@ -6605,22 +6583,22 @@
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="C26" s="3">
-        <v>46197</v>
+        <v>46288</v>
       </c>
       <c r="D26" s="4">
-        <v>563362114</v>
+        <v>563362999</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6">
-        <v>46108</v>
+        <v>46094</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>104</v>
@@ -6632,25 +6610,25 @@
         <v>42</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="K26" s="3">
-        <v>46148</v>
+        <v>46286</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-102</v>
+        <f ca="1">IF($O26="","",$O26-TODAY())</f>
+        <v>-116</v>
       </c>
       <c r="M26" s="12">
         <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="N26" s="12">
         <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>262</v>
+        <v>353</v>
       </c>
       <c r="O26" s="6">
-        <v>46198</v>
+        <v>46184</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>97</v>
@@ -6688,23 +6666,23 @@
         <v>0</v>
       </c>
       <c r="AC26" s="6">
-        <v>46197</v>
+        <v>46223</v>
       </c>
       <c r="AD26" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE26" s="4">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="AF26" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AG26" s="5"/>
       <c r="AH26" s="5"/>
       <c r="AI26" s="5"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AL26" s="5" t="s">
         <v>60</v>
@@ -6718,28 +6696,28 @@
     </row>
     <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>407</v>
+        <v>347</v>
       </c>
       <c r="C27" s="3">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D27" s="4">
-        <v>553283455</v>
+        <v>553362911</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F27" s="6">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>42</v>
@@ -6748,37 +6726,37 @@
         <v>78</v>
       </c>
       <c r="K27" s="3">
-        <v>46300</v>
+        <v>46266</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-80</v>
+        <f ca="1">IF($O27="","",$O27-TODAY())</f>
+        <v>-109</v>
       </c>
       <c r="M27" s="12">
-        <f ca="1">IF($C27="","",$C27+180-TODAY())</f>
-        <v>64</v>
+        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
+        <v>250</v>
       </c>
       <c r="N27" s="12">
-        <f ca="1">IF($C27="","",$C27+180-TODAY())</f>
-        <v>64</v>
+        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
+        <v>250</v>
       </c>
       <c r="O27" s="6">
-        <v>46220</v>
+        <v>46191</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="R27" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="S27" s="5" t="s">
         <v>47</v>
       </c>
       <c r="T27" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="U27" s="5" t="s">
         <v>47</v>
@@ -6793,29 +6771,29 @@
         <v>1426.25</v>
       </c>
       <c r="AA27" s="7">
-        <v>0</v>
+        <v>1245.54</v>
       </c>
       <c r="AB27" s="7">
-        <v>0</v>
+        <v>361.42</v>
       </c>
       <c r="AC27" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="AD27" s="7">
-        <v>1426.25</v>
+        <v>-180.71</v>
       </c>
       <c r="AE27" s="4">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF27" s="5" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="AG27" s="5"/>
       <c r="AH27" s="5"/>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="AL27" s="5" t="s">
         <v>73</v>
@@ -6829,58 +6807,58 @@
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C28" s="3">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="D28" s="4">
-        <v>554404221</v>
+        <v>555169750</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6">
-        <v>46112</v>
+        <v>46104</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="K28" s="3">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-68</v>
+        <f ca="1">IF($O28="","",$O28-TODAY())</f>
+        <v>-106</v>
       </c>
       <c r="M28" s="12">
         <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="N28" s="12">
-        <f ca="1">IF($C28="","",$C28+90-TODAY())</f>
-        <v>-82</v>
+        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
+        <v>206</v>
       </c>
       <c r="O28" s="6">
-        <v>46232</v>
+        <v>46194</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="R28" s="5" t="s">
         <v>57</v>
@@ -6889,7 +6867,7 @@
         <v>47</v>
       </c>
       <c r="T28" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="U28" s="5" t="s">
         <v>47</v>
@@ -6901,7 +6879,7 @@
         <v>48</v>
       </c>
       <c r="Z28" s="7">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="AA28" s="7">
         <v>0</v>
@@ -6910,29 +6888,31 @@
         <v>0</v>
       </c>
       <c r="AC28" s="6">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="AD28" s="7">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="AE28" s="4">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="AF28" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG28" s="5"/>
+        <v>121</v>
+      </c>
+      <c r="AG28" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="AH28" s="5"/>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="AL28" s="5" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="AM28" s="6">
-        <v>46119</v>
+        <v>46105</v>
       </c>
       <c r="AN28" s="5" t="s">
         <v>52</v>
@@ -6940,53 +6920,71 @@
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C29" s="3">
-        <v>46128</v>
+        <v>46123</v>
       </c>
       <c r="D29" s="4">
-        <v>553124954</v>
+        <v>554246495</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F29" s="6">
-        <v>46099</v>
+        <v>46106</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="K29" s="3">
-        <v>46269</v>
-      </c>
-      <c r="L29" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="5"/>
+        <v>46268</v>
+      </c>
+      <c r="L29" s="12">
+        <f ca="1">IF($O29="","",$O29-TODAY())</f>
+        <v>-104</v>
+      </c>
+      <c r="M29" s="12">
+        <f ca="1">IF($F29="","",$F29+90-TODAY())</f>
+        <v>-104</v>
+      </c>
+      <c r="N29" s="12">
+        <f ca="1">IF($C29="","",$C29+540-TODAY())</f>
+        <v>363</v>
+      </c>
+      <c r="O29" s="6">
+        <v>46196</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>97</v>
+      </c>
       <c r="Q29" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="5"/>
+        <v>127</v>
+      </c>
+      <c r="R29" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="S29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T29" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="U29" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="V29" s="5"/>
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
@@ -6994,32 +6992,34 @@
         <v>48</v>
       </c>
       <c r="Z29" s="7">
-        <v>1372.91</v>
+        <v>1029.98</v>
       </c>
       <c r="AA29" s="7">
-        <v>0</v>
+        <v>883.53</v>
       </c>
       <c r="AB29" s="7">
-        <v>0</v>
+        <v>121.45</v>
       </c>
       <c r="AC29" s="6">
-        <v>46128</v>
+        <v>46123</v>
       </c>
       <c r="AD29" s="7">
-        <v>1372.91</v>
+        <v>25</v>
       </c>
       <c r="AE29" s="4">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="AF29" s="5" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="AG29" s="5"/>
       <c r="AH29" s="5"/>
       <c r="AI29" s="5"/>
-      <c r="AJ29" s="4"/>
+      <c r="AJ29" s="4">
+        <v>557570817</v>
+      </c>
       <c r="AK29" s="5" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="AL29" s="5" t="s">
         <v>73</v>
@@ -7066,7 +7066,7 @@
         <v>46269</v>
       </c>
       <c r="L30" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O30="","",$O30-TODAY())</f>
         <v/>
       </c>
       <c r="M30" s="12"/>
@@ -7398,22 +7398,22 @@
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C2" s="3">
-        <v>46141</v>
+        <v>46122</v>
       </c>
       <c r="D2" s="4">
-        <v>551735634</v>
+        <v>554946837</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="F2" s="6">
-        <v>46085</v>
+        <v>46104</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>147</v>
@@ -7422,28 +7422,28 @@
         <v>147</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K2" s="3">
         <v>46300</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L11" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
-        <v>150</v>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
+        <v>169</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M10" ca="1" si="1">IF($C2="","",$C2+365-TODAY())</f>
-        <v>206</v>
+        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <v>187</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N8" ca="1" si="2">IF($C2="","",$C2+120-TODAY())</f>
-        <v>-39</v>
+        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
+        <v>-58</v>
       </c>
       <c r="O2" s="6">
-        <v>46450</v>
+        <v>46469</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>57</v>
@@ -7472,7 +7472,7 @@
         <v>48</v>
       </c>
       <c r="Z2" s="7">
-        <v>4520.1099999999997</v>
+        <v>6392.96</v>
       </c>
       <c r="AA2" s="7">
         <v>0</v>
@@ -7481,29 +7481,33 @@
         <v>0</v>
       </c>
       <c r="AC2" s="6">
-        <v>46141</v>
+        <v>46122</v>
       </c>
       <c r="AD2" s="7">
-        <v>4520.1099999999997</v>
+        <v>6392.96</v>
       </c>
       <c r="AE2" s="4">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
+        <v>170</v>
+      </c>
+      <c r="AG2" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="5" t="s">
         <v>152</v>
       </c>
       <c r="AL2" s="5" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="AM2" s="6">
-        <v>46099</v>
+        <v>46118</v>
       </c>
       <c r="AN2" s="5" t="s">
         <v>154</v>
@@ -7511,73 +7515,73 @@
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C3" s="3">
-        <v>46121</v>
+        <v>46216</v>
       </c>
       <c r="D3" s="4">
-        <v>553103783</v>
+        <v>554940052</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="F3" s="6">
-        <v>46097</v>
+        <v>46107</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="K3" s="3">
         <v>46300</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>162</v>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
+        <v>-103</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>186</v>
+        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <v>96</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-59</v>
+        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <v>281</v>
       </c>
       <c r="O3" s="6">
-        <v>46462</v>
+        <v>46197</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="S3" s="5" t="s">
         <v>47</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>47</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
@@ -7588,37 +7592,41 @@
         <v>6392.96</v>
       </c>
       <c r="AA3" s="7">
-        <v>0</v>
+        <v>5793.21</v>
       </c>
       <c r="AB3" s="7">
         <v>0</v>
       </c>
       <c r="AC3" s="6">
-        <v>46121</v>
+        <v>46216</v>
       </c>
       <c r="AD3" s="7">
-        <v>6392.96</v>
+        <v>599.75</v>
       </c>
       <c r="AE3" s="4">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="AF3" s="5" t="s">
         <v>158</v>
       </c>
       <c r="AG3" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="AH3" s="5"/>
+        <v>189</v>
+      </c>
+      <c r="AH3" s="5" t="s">
+        <v>198</v>
+      </c>
       <c r="AI3" s="5"/>
-      <c r="AJ3" s="4"/>
+      <c r="AJ3" s="4">
+        <v>561872992</v>
+      </c>
       <c r="AK3" s="5" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="AM3" s="6">
-        <v>46099</v>
+        <v>46118</v>
       </c>
       <c r="AN3" s="5" t="s">
         <v>154</v>
@@ -7629,19 +7637,19 @@
         <v>61</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
       <c r="C4" s="3">
-        <v>46249</v>
+        <v>46141</v>
       </c>
       <c r="D4" s="4">
-        <v>557717115</v>
+        <v>551735634</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F4" s="6">
-        <v>46097</v>
+        <v>46085</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>147</v>
@@ -7650,28 +7658,28 @@
         <v>147</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="K4" s="3">
-        <v>46261</v>
+        <v>46300</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>162</v>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
+        <v>150</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>314</v>
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <v>206</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>69</v>
+        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <v>-39</v>
       </c>
       <c r="O4" s="6">
-        <v>46462</v>
+        <v>46450</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>57</v>
@@ -7692,48 +7700,46 @@
         <v>47</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
       <c r="Y4" s="5" t="s">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="Z4" s="7">
-        <v>18176.900000000001</v>
+        <v>4520.1099999999997</v>
       </c>
       <c r="AA4" s="7">
         <v>0</v>
       </c>
       <c r="AB4" s="7">
-        <v>542.44000000000005</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="6">
-        <v>46165</v>
+        <v>46141</v>
       </c>
       <c r="AD4" s="7">
-        <v>17634.46</v>
+        <v>4520.1099999999997</v>
       </c>
       <c r="AE4" s="4">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="AG4" s="5" t="s">
-        <v>167</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="AG4" s="5"/>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="AL4" s="5" t="s">
         <v>153</v>
       </c>
       <c r="AM4" s="6">
-        <v>46115</v>
+        <v>46099</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>154</v>
@@ -7741,22 +7747,22 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C5" s="3">
-        <v>46122</v>
+        <v>46121</v>
       </c>
       <c r="D5" s="4">
-        <v>554946837</v>
+        <v>553103783</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="F5" s="6">
-        <v>46104</v>
+        <v>46097</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>147</v>
@@ -7774,19 +7780,19 @@
         <v>46300</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>169</v>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
+        <v>162</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>187</v>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <v>186</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-58</v>
+        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <v>-59</v>
       </c>
       <c r="O5" s="6">
-        <v>46469</v>
+        <v>46462</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>57</v>
@@ -7824,33 +7830,31 @@
         <v>0</v>
       </c>
       <c r="AC5" s="6">
-        <v>46122</v>
+        <v>46121</v>
       </c>
       <c r="AD5" s="7">
         <v>6392.96</v>
       </c>
       <c r="AE5" s="4">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="AH5" s="5" t="s">
         <v>159</v>
       </c>
+      <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
         <v>152</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="AM5" s="6">
-        <v>46118</v>
+        <v>46099</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>154</v>
@@ -7861,49 +7865,49 @@
         <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>403</v>
+        <v>342</v>
       </c>
       <c r="C6" s="3">
-        <v>46156</v>
+        <v>46249</v>
       </c>
       <c r="D6" s="4">
-        <v>556757813</v>
+        <v>557717115</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F6" s="6">
-        <v>46104</v>
+        <v>46097</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="K6" s="3">
-        <v>46300</v>
+        <v>46261</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>169</v>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
+        <v>162</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>221</v>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <v>314</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-24</v>
+        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <v>69</v>
       </c>
       <c r="O6" s="6">
-        <v>46469</v>
+        <v>46462</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>57</v>
@@ -7924,48 +7928,48 @@
         <v>47</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="Z6" s="7">
-        <v>36353.800000000003</v>
+        <v>18176.900000000001</v>
       </c>
       <c r="AA6" s="7">
         <v>0</v>
       </c>
       <c r="AB6" s="7">
-        <v>0</v>
+        <v>542.44000000000005</v>
       </c>
       <c r="AC6" s="6">
-        <v>46156</v>
+        <v>46165</v>
       </c>
       <c r="AD6" s="7">
-        <v>36353.800000000003</v>
+        <v>17634.46</v>
       </c>
       <c r="AE6" s="4">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="AF6" s="5" t="s">
         <v>166</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="AM6" s="6">
-        <v>46133</v>
+        <v>46115</v>
       </c>
       <c r="AN6" s="5" t="s">
         <v>154</v>
@@ -7976,49 +7980,49 @@
         <v>61</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>342</v>
+        <v>403</v>
       </c>
       <c r="C7" s="3">
-        <v>46249</v>
+        <v>46156</v>
       </c>
       <c r="D7" s="4">
-        <v>556761529</v>
+        <v>556757813</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F7" s="6">
-        <v>46111</v>
+        <v>46104</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="K7" s="3">
-        <v>46261</v>
+        <v>46300</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>176</v>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
+        <v>169</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>314</v>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <v>221</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>69</v>
+        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
+        <v>-24</v>
       </c>
       <c r="O7" s="6">
-        <v>46476</v>
+        <v>46469</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>57</v>
@@ -8044,25 +8048,25 @@
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="Z7" s="7">
-        <v>18176.900000000001</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA7" s="7">
         <v>0</v>
       </c>
       <c r="AB7" s="7">
-        <v>542.44000000000005</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="6">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="AD7" s="7">
-        <v>17634.46</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AE7" s="4">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="AF7" s="5" t="s">
         <v>166</v>
@@ -8074,10 +8078,10 @@
       <c r="AI7" s="5"/>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
-        <v>168</v>
+        <v>87</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="AM7" s="6">
         <v>46133</v>
@@ -8091,19 +8095,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>404</v>
+        <v>342</v>
       </c>
       <c r="C8" s="3">
-        <v>46121</v>
+        <v>46249</v>
       </c>
       <c r="D8" s="4">
-        <v>554941943</v>
+        <v>556761529</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F8" s="6">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>147</v>
@@ -8112,28 +8116,28 @@
         <v>147</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>182</v>
+        <v>70</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="K8" s="3">
-        <v>46300</v>
+        <v>46261</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>177</v>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
+        <v>176</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>186</v>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v>314</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-59</v>
+        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
+        <v>69</v>
       </c>
       <c r="O8" s="6">
-        <v>46477</v>
+        <v>46476</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>57</v>
@@ -8154,50 +8158,48 @@
         <v>47</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="Z8" s="7">
-        <v>6392.96</v>
+        <v>18176.900000000001</v>
       </c>
       <c r="AA8" s="7">
         <v>0</v>
       </c>
       <c r="AB8" s="7">
-        <v>0</v>
+        <v>542.44000000000005</v>
       </c>
       <c r="AC8" s="6">
-        <v>46121</v>
+        <v>46154</v>
       </c>
       <c r="AD8" s="7">
-        <v>6392.96</v>
+        <v>17634.46</v>
       </c>
       <c r="AE8" s="4">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AF8" s="5" t="s">
         <v>166</v>
       </c>
       <c r="AG8" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="AH8" s="5" t="s">
-        <v>184</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="AM8" s="6">
-        <v>46118</v>
+        <v>46133</v>
       </c>
       <c r="AN8" s="5" t="s">
         <v>154</v>
@@ -8208,55 +8210,55 @@
         <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="C9" s="3">
-        <v>46129</v>
+        <v>46121</v>
       </c>
       <c r="D9" s="4">
-        <v>555728365</v>
+        <v>554941943</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46112</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="K9" s="3">
+        <v>46300</v>
+      </c>
+      <c r="L9" s="12">
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
+        <v>177</v>
+      </c>
+      <c r="M9" s="12">
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
         <v>186</v>
       </c>
-      <c r="F9" s="6">
-        <v>46092</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="K9" s="3">
-        <v>46257</v>
-      </c>
-      <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-118</v>
-      </c>
-      <c r="M9" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>194</v>
-      </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>194</v>
+        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <v>-59</v>
       </c>
       <c r="O9" s="6">
-        <v>46182</v>
+        <v>46477</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="R9" s="5" t="s">
         <v>57</v>
@@ -8265,13 +8267,13 @@
         <v>47</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>47</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
@@ -8287,30 +8289,34 @@
       <c r="AB9" s="7">
         <v>0</v>
       </c>
-      <c r="AC9" s="6"/>
+      <c r="AC9" s="6">
+        <v>46121</v>
+      </c>
       <c r="AD9" s="7">
         <v>6392.96</v>
       </c>
       <c r="AE9" s="4">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="AH9" s="5"/>
+        <v>183</v>
+      </c>
+      <c r="AH9" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="AM9" s="6">
-        <v>46125</v>
+        <v>46118</v>
       </c>
       <c r="AN9" s="5" t="s">
         <v>154</v>
@@ -8321,19 +8327,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C10" s="3">
-        <v>46227</v>
+        <v>46129</v>
       </c>
       <c r="D10" s="4">
-        <v>552871981</v>
+        <v>555728365</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F10" s="6">
-        <v>46097</v>
+        <v>46092</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>101</v>
@@ -8345,25 +8351,25 @@
         <v>42</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K10" s="3">
-        <v>46245</v>
+        <v>46257</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-113</v>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
+        <v>-118</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>292</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>194</v>
       </c>
       <c r="N10" s="12">
         <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>292</v>
+        <v>194</v>
       </c>
       <c r="O10" s="6">
-        <v>46187</v>
+        <v>46182</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>97</v>
@@ -8384,15 +8390,15 @@
         <v>47</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="5" t="s">
-        <v>177</v>
+        <v>48</v>
       </c>
       <c r="Z10" s="7">
-        <v>5916.4</v>
+        <v>6392.96</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -8402,30 +8408,28 @@
       </c>
       <c r="AC10" s="6"/>
       <c r="AD10" s="7">
-        <v>5916.4</v>
+        <v>6392.96</v>
       </c>
       <c r="AE10" s="4">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="AG10" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="AH10" s="5" t="s">
-        <v>194</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="AL10" s="5" t="s">
         <v>73</v>
       </c>
       <c r="AM10" s="6">
-        <v>46217</v>
+        <v>46125</v>
       </c>
       <c r="AN10" s="5" t="s">
         <v>154</v>
@@ -8433,61 +8437,61 @@
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="C11" s="3">
-        <v>46216</v>
+        <v>46227</v>
       </c>
       <c r="D11" s="4">
-        <v>554940052</v>
+        <v>552871981</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F11" s="6">
-        <v>46107</v>
+        <v>46097</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>197</v>
+        <v>101</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>197</v>
+        <v>42</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K11" s="3">
-        <v>46300</v>
+        <v>46245</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-103</v>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
+        <v>-113</v>
       </c>
       <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
-        <v>96</v>
+        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <v>292</v>
       </c>
       <c r="N11" s="12">
         <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="O11" s="6">
-        <v>46197</v>
+        <v>46187</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>97</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="S11" s="5" t="s">
         <v>47</v>
@@ -8499,52 +8503,48 @@
         <v>47</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="5" t="s">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="Z11" s="7">
-        <v>6392.96</v>
+        <v>5916.4</v>
       </c>
       <c r="AA11" s="7">
-        <v>5793.21</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="7">
         <v>0</v>
       </c>
-      <c r="AC11" s="6">
-        <v>46216</v>
-      </c>
+      <c r="AC11" s="6"/>
       <c r="AD11" s="7">
-        <v>599.75</v>
+        <v>5916.4</v>
       </c>
       <c r="AE11" s="4">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="AG11" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AH11" s="5" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="AI11" s="5"/>
-      <c r="AJ11" s="4">
-        <v>561872992</v>
-      </c>
+      <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AL11" s="5" t="s">
         <v>73</v>
       </c>
       <c r="AM11" s="6">
-        <v>46118</v>
+        <v>46217</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>154</v>
@@ -9324,64 +9324,62 @@
         <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C2" s="3">
-        <v>46107</v>
+        <v>46204</v>
       </c>
       <c r="D2" s="4">
-        <v>553613990</v>
+        <v>552284225</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="F2" s="6">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>64</v>
+        <v>252</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>64</v>
+        <v>252</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="K2" s="3">
-        <v>46279</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="K2" s="3"/>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L14" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
-        <v>148</v>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
+        <v>-125</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M7" ca="1" si="1">IF($C2="","",$C2+365-TODAY())</f>
-        <v>172</v>
+        <f ca="1">IF($F2="","",$F2+90-TODAY())</f>
+        <v>-125</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N7" ca="1" si="2">IF($C2="","",$C2+120-TODAY())</f>
-        <v>-73</v>
+        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <v>84</v>
       </c>
       <c r="O2" s="6">
-        <v>46448</v>
+        <v>46175</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>66</v>
+        <v>254</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>47</v>
@@ -9393,7 +9391,7 @@
         <v>48</v>
       </c>
       <c r="Z2" s="7">
-        <v>5784.24</v>
+        <v>1433.32</v>
       </c>
       <c r="AA2" s="7">
         <v>0</v>
@@ -9402,31 +9400,35 @@
         <v>0</v>
       </c>
       <c r="AC2" s="6">
-        <v>46107</v>
+        <v>46204</v>
       </c>
       <c r="AD2" s="7">
-        <v>5784.24</v>
+        <v>1433.32</v>
       </c>
       <c r="AE2" s="4">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="AG2" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="AH2" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
+      <c r="AI2" s="5" t="s">
+        <v>255</v>
+      </c>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="5" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AL2" s="5" t="s">
         <v>211</v>
       </c>
       <c r="AM2" s="6">
-        <v>46105</v>
+        <v>46197</v>
       </c>
       <c r="AN2" s="5" t="s">
         <v>226</v>
@@ -9436,20 +9438,20 @@
       <c r="A3" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>376</v>
+      <c r="B3" s="2" t="s">
+        <v>374</v>
       </c>
       <c r="C3" s="3">
-        <v>46203</v>
+        <v>46107</v>
       </c>
       <c r="D3" s="4">
-        <v>552282896</v>
+        <v>553613990</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F3" s="6">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>64</v>
@@ -9458,28 +9460,28 @@
         <v>64</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K3" s="3">
         <v>46279</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>150</v>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
+        <v>148</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>268</v>
+        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <v>172</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>23</v>
+        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
+        <v>-73</v>
       </c>
       <c r="O3" s="6">
-        <v>46450</v>
+        <v>46448</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>57</v>
@@ -9506,7 +9508,7 @@
         <v>48</v>
       </c>
       <c r="Z3" s="7">
-        <v>9056.39</v>
+        <v>5784.24</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
@@ -9515,35 +9517,31 @@
         <v>0</v>
       </c>
       <c r="AC3" s="6">
-        <v>46203</v>
+        <v>46107</v>
       </c>
       <c r="AD3" s="7">
-        <v>9056.39</v>
+        <v>5784.24</v>
       </c>
       <c r="AE3" s="4">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="AG3" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="AH3" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="AI3" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="5" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AL3" s="5" t="s">
         <v>211</v>
       </c>
       <c r="AM3" s="6">
-        <v>46197</v>
+        <v>46105</v>
       </c>
       <c r="AN3" s="5" t="s">
         <v>226</v>
@@ -9551,22 +9549,22 @@
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>375</v>
+        <v>200</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>376</v>
       </c>
       <c r="C4" s="3">
-        <v>46108</v>
+        <v>46203</v>
       </c>
       <c r="D4" s="4">
-        <v>553223068</v>
+        <v>552282896</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="F4" s="6">
-        <v>46099</v>
+        <v>46085</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>64</v>
@@ -9578,25 +9576,25 @@
         <v>70</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="K4" s="3">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>164</v>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
+        <v>150</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>173</v>
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <v>268</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-72</v>
+        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <v>23</v>
       </c>
       <c r="O4" s="6">
-        <v>46464</v>
+        <v>46450</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>57</v>
@@ -9623,7 +9621,7 @@
         <v>48</v>
       </c>
       <c r="Z4" s="7">
-        <v>2493.33</v>
+        <v>9056.39</v>
       </c>
       <c r="AA4" s="7">
         <v>0</v>
@@ -9632,31 +9630,35 @@
         <v>0</v>
       </c>
       <c r="AC4" s="6">
-        <v>46108</v>
+        <v>46203</v>
       </c>
       <c r="AD4" s="7">
-        <v>2493.33</v>
+        <v>9056.39</v>
       </c>
       <c r="AE4" s="4">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AG4" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
+        <v>230</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>232</v>
+      </c>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="AM4" s="6">
-        <v>46101</v>
+        <v>46197</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>226</v>
@@ -9664,22 +9666,22 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>200</v>
+        <v>354</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C5" s="3">
-        <v>46203</v>
+        <v>46108</v>
       </c>
       <c r="D5" s="4">
-        <v>555372244</v>
+        <v>553223068</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F5" s="6">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>64</v>
@@ -9691,25 +9693,25 @@
         <v>70</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="K5" s="3">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>169</v>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
+        <v>164</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>268</v>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <v>173</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>23</v>
+        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <v>-72</v>
       </c>
       <c r="O5" s="6">
-        <v>46469</v>
+        <v>46464</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>57</v>
@@ -9729,16 +9731,14 @@
       <c r="U5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V5" s="5" t="s">
-        <v>242</v>
-      </c>
+      <c r="V5" s="5"/>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
       <c r="Y5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z5" s="7">
-        <v>19949.23</v>
+        <v>2493.33</v>
       </c>
       <c r="AA5" s="7">
         <v>0</v>
@@ -9747,35 +9747,31 @@
         <v>0</v>
       </c>
       <c r="AC5" s="6">
-        <v>46203</v>
+        <v>46108</v>
       </c>
       <c r="AD5" s="7">
-        <v>19949.23</v>
+        <v>2493.33</v>
       </c>
       <c r="AE5" s="4">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="AH5" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI5" s="5" t="s">
-        <v>158</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="AM5" s="6">
-        <v>46197</v>
+        <v>46101</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>226</v>
@@ -9783,52 +9779,52 @@
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>354</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C6" s="3">
-        <v>46122</v>
+        <v>46203</v>
       </c>
       <c r="D6" s="4">
-        <v>553825634</v>
+        <v>555372244</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F6" s="6">
-        <v>46106</v>
+        <v>46104</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>64</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="K6" s="3">
         <v>46279</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>171</v>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
+        <v>169</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>187</v>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <v>268</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-58</v>
+        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <v>23</v>
       </c>
       <c r="O6" s="6">
-        <v>46471</v>
+        <v>46469</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>57</v>
@@ -9848,47 +9844,53 @@
       <c r="U6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V6" s="5"/>
+      <c r="V6" s="5" t="s">
+        <v>242</v>
+      </c>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z6" s="7">
-        <v>2493.33</v>
+        <v>19949.23</v>
       </c>
       <c r="AA6" s="7">
-        <v>2351.73</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="7">
-        <v>110.6</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="6">
-        <v>46122</v>
+        <v>46203</v>
       </c>
       <c r="AD6" s="7">
-        <v>31</v>
+        <v>19949.23</v>
       </c>
       <c r="AE6" s="4">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="AG6" s="5"/>
-      <c r="AH6" s="5"/>
-      <c r="AI6" s="5"/>
-      <c r="AJ6" s="4">
-        <v>557571095</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="AG6" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="AH6" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI6" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>84</v>
+        <v>233</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="AM6" s="6">
-        <v>46107</v>
+        <v>46197</v>
       </c>
       <c r="AN6" s="5" t="s">
         <v>226</v>
@@ -9902,46 +9904,46 @@
         <v>378</v>
       </c>
       <c r="C7" s="3">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="D7" s="4">
-        <v>554186385</v>
+        <v>553825634</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F7" s="6">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>248</v>
+        <v>86</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>64</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>248</v>
+        <v>86</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="K7" s="3">
         <v>46279</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>173</v>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
+        <v>171</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>191</v>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <v>187</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-54</v>
+        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
+        <v>-58</v>
       </c>
       <c r="O7" s="6">
-        <v>46473</v>
+        <v>46471</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>57</v>
@@ -9961,49 +9963,47 @@
       <c r="U7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V7" s="5" t="s">
-        <v>221</v>
-      </c>
+      <c r="V7" s="5"/>
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z7" s="7">
-        <v>5614.63</v>
+        <v>2493.33</v>
       </c>
       <c r="AA7" s="7">
-        <v>4889.05</v>
+        <v>2351.73</v>
       </c>
       <c r="AB7" s="7">
-        <v>578.1</v>
+        <v>110.6</v>
       </c>
       <c r="AC7" s="6">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="AD7" s="7">
-        <v>147.47999999999999</v>
+        <v>31</v>
       </c>
       <c r="AE7" s="4">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
       <c r="AJ7" s="4">
-        <v>557570916</v>
+        <v>557571095</v>
       </c>
       <c r="AK7" s="5" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="AM7" s="6">
-        <v>46112</v>
+        <v>46107</v>
       </c>
       <c r="AN7" s="5" t="s">
         <v>226</v>
@@ -10011,114 +10011,114 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>354</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C8" s="3">
-        <v>46204</v>
+        <v>46126</v>
       </c>
       <c r="D8" s="4">
-        <v>552284225</v>
+        <v>554186385</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F8" s="6">
-        <v>46085</v>
+        <v>46108</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>252</v>
+        <v>64</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>42</v>
+        <v>248</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="K8" s="3"/>
+        <v>249</v>
+      </c>
+      <c r="K8" s="3">
+        <v>46279</v>
+      </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-125</v>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
+        <v>173</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($F8="","",$F8+90-TODAY())</f>
-        <v>-125</v>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v>191</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
-        <v>84</v>
+        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
+        <v>-54</v>
       </c>
       <c r="O8" s="6">
-        <v>46175</v>
+        <v>46473</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>254</v>
+        <v>66</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V8" s="5"/>
+      <c r="V8" s="5" t="s">
+        <v>221</v>
+      </c>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z8" s="7">
-        <v>1433.32</v>
+        <v>5614.63</v>
       </c>
       <c r="AA8" s="7">
-        <v>0</v>
+        <v>4889.05</v>
       </c>
       <c r="AB8" s="7">
-        <v>0</v>
+        <v>578.1</v>
       </c>
       <c r="AC8" s="6">
-        <v>46204</v>
+        <v>46126</v>
       </c>
       <c r="AD8" s="7">
-        <v>1433.32</v>
+        <v>147.47999999999999</v>
       </c>
       <c r="AE8" s="4">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="AG8" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="AH8" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="AI8" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="AJ8" s="4"/>
+        <v>250</v>
+      </c>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5"/>
+      <c r="AI8" s="5"/>
+      <c r="AJ8" s="4">
+        <v>557570916</v>
+      </c>
       <c r="AK8" s="5" t="s">
-        <v>233</v>
+        <v>119</v>
       </c>
       <c r="AL8" s="5" t="s">
         <v>211</v>
       </c>
       <c r="AM8" s="6">
-        <v>46197</v>
+        <v>46112</v>
       </c>
       <c r="AN8" s="5" t="s">
         <v>226</v>
@@ -10159,7 +10159,7 @@
         <v>46279</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
         <v>-123</v>
       </c>
       <c r="M9" s="12">
@@ -10237,56 +10237,58 @@
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>342</v>
+        <v>200</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="C10" s="3">
-        <v>46203</v>
+        <v>46108</v>
       </c>
       <c r="D10" s="4">
-        <v>553643849</v>
+        <v>553652690</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F10" s="6">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="K10" s="3"/>
+        <v>266</v>
+      </c>
+      <c r="K10" s="3">
+        <v>46265</v>
+      </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-123</v>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
+        <v>-117</v>
       </c>
       <c r="M10" s="12">
         <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
-        <v>-123</v>
+        <v>-117</v>
       </c>
       <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>268</v>
+        <f ca="1">IF($C10="","",$C10+540-TODAY())</f>
+        <v>348</v>
       </c>
       <c r="O10" s="6">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>97</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="R10" s="5" t="s">
         <v>97</v>
@@ -10295,7 +10297,7 @@
         <v>46</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>57</v>
+        <v>393</v>
       </c>
       <c r="U10" s="5" t="s">
         <v>47</v>
@@ -10317,18 +10319,20 @@
       <c r="AB10" s="7">
         <v>0</v>
       </c>
-      <c r="AC10" s="6"/>
+      <c r="AC10" s="6">
+        <v>46108</v>
+      </c>
       <c r="AD10" s="7">
         <v>18400.34</v>
       </c>
       <c r="AE10" s="4">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="AG10" s="5" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
@@ -10340,7 +10344,7 @@
         <v>264</v>
       </c>
       <c r="AM10" s="6">
-        <v>46197</v>
+        <v>46105</v>
       </c>
       <c r="AN10" s="5" t="s">
         <v>226</v>
@@ -10351,16 +10355,16 @@
         <v>200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C11" s="3">
-        <v>46108</v>
+        <v>46220</v>
       </c>
       <c r="D11" s="4">
-        <v>553652690</v>
+        <v>553656838</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F11" s="6">
         <v>46093</v>
@@ -10375,13 +10379,13 @@
         <v>42</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K11" s="3">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
         <v>-117</v>
       </c>
       <c r="M11" s="12">
@@ -10390,7 +10394,7 @@
       </c>
       <c r="N11" s="12">
         <f ca="1">IF($C11="","",$C11+540-TODAY())</f>
-        <v>348</v>
+        <v>460</v>
       </c>
       <c r="O11" s="6">
         <v>46183</v>
@@ -10413,16 +10417,14 @@
       <c r="U11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V11" s="5" t="s">
-        <v>260</v>
-      </c>
+      <c r="V11" s="5"/>
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z11" s="7">
-        <v>18400.34</v>
+        <v>12650.96</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -10431,10 +10433,10 @@
         <v>0</v>
       </c>
       <c r="AC11" s="6">
-        <v>46108</v>
+        <v>46220</v>
       </c>
       <c r="AD11" s="7">
-        <v>18400.34</v>
+        <v>12650.96</v>
       </c>
       <c r="AE11" s="4">
         <v>149</v>
@@ -10443,7 +10445,7 @@
         <v>158</v>
       </c>
       <c r="AG11" s="5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
@@ -10466,46 +10468,46 @@
         <v>200</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C12" s="3">
-        <v>46220</v>
+        <v>46127</v>
       </c>
       <c r="D12" s="4">
-        <v>553656838</v>
+        <v>555351211</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F12" s="6">
         <v>46093</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K12" s="3">
         <v>46279</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
         <v>-117</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($F12="","",$F12+90-TODAY())</f>
-        <v>-117</v>
+        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <v>7</v>
       </c>
       <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+540-TODAY())</f>
-        <v>460</v>
+        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <v>192</v>
       </c>
       <c r="O12" s="6">
         <v>46183</v>
@@ -10514,16 +10516,16 @@
         <v>97</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>393</v>
+        <v>57</v>
       </c>
       <c r="U12" s="5" t="s">
         <v>47</v>
@@ -10535,7 +10537,7 @@
         <v>48</v>
       </c>
       <c r="Z12" s="7">
-        <v>12650.96</v>
+        <v>8277.57</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -10544,31 +10546,31 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46220</v>
+        <v>46127</v>
       </c>
       <c r="AD12" s="7">
-        <v>12650.96</v>
+        <v>8277.57</v>
       </c>
       <c r="AE12" s="4">
         <v>149</v>
       </c>
       <c r="AF12" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG12" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="AG12" s="5" t="s">
-        <v>270</v>
       </c>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="AM12" s="6">
-        <v>46105</v>
+        <v>46120</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>226</v>
@@ -10576,58 +10578,58 @@
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>200</v>
+        <v>354</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C13" s="3">
-        <v>46127</v>
+        <v>46163</v>
       </c>
       <c r="D13" s="4">
-        <v>555351211</v>
+        <v>553378154</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F13" s="6">
-        <v>46093</v>
+        <v>46101</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="K13" s="3">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-117</v>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
+        <v>-79</v>
       </c>
       <c r="M13" s="12">
         <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v>192</v>
+        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <v>43</v>
       </c>
       <c r="O13" s="6">
-        <v>46183</v>
+        <v>46221</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>111</v>
+        <v>275</v>
       </c>
       <c r="R13" s="5" t="s">
         <v>44</v>
@@ -10636,7 +10638,7 @@
         <v>47</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>47</v>
@@ -10648,7 +10650,7 @@
         <v>48</v>
       </c>
       <c r="Z13" s="7">
-        <v>8277.57</v>
+        <v>7623.07</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -10657,31 +10659,29 @@
         <v>0</v>
       </c>
       <c r="AC13" s="6">
-        <v>46127</v>
+        <v>46163</v>
       </c>
       <c r="AD13" s="7">
-        <v>8277.57</v>
+        <v>7623.07</v>
       </c>
       <c r="AE13" s="4">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="AG13" s="5" t="s">
-        <v>158</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="AG13" s="5"/>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>225</v>
+        <v>84</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="AM13" s="6">
-        <v>46120</v>
+        <v>46105</v>
       </c>
       <c r="AN13" s="5" t="s">
         <v>226</v>
@@ -10689,79 +10689,79 @@
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
       <c r="C14" s="3">
-        <v>46163</v>
+        <v>46203</v>
       </c>
       <c r="D14" s="4">
-        <v>553378154</v>
+        <v>553643849</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="F14" s="6">
-        <v>46101</v>
+        <v>46087</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>274</v>
+        <v>70</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>274</v>
+        <v>70</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="K14" s="3">
-        <v>46268</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="K14" s="3"/>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-79</v>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
+        <v>-123</v>
       </c>
       <c r="M14" s="12">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
-        <v>43</v>
+        <f ca="1">IF($F14="","",$F14+90-TODAY())</f>
+        <v>-123</v>
       </c>
       <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
-        <v>43</v>
+        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <v>268</v>
       </c>
       <c r="O14" s="6">
-        <v>46221</v>
+        <v>46177</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>275</v>
+        <v>98</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="U14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V14" s="5"/>
+      <c r="V14" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z14" s="7">
-        <v>7623.07</v>
+        <v>18400.34</v>
       </c>
       <c r="AA14" s="7">
         <v>0</v>
@@ -10769,30 +10769,30 @@
       <c r="AB14" s="7">
         <v>0</v>
       </c>
-      <c r="AC14" s="6">
-        <v>46163</v>
-      </c>
+      <c r="AC14" s="6"/>
       <c r="AD14" s="7">
-        <v>7623.07</v>
+        <v>18400.34</v>
       </c>
       <c r="AE14" s="4">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="AG14" s="5"/>
+        <v>261</v>
+      </c>
+      <c r="AG14" s="5" t="s">
+        <v>262</v>
+      </c>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="AM14" s="6">
-        <v>46105</v>
+        <v>46197</v>
       </c>
       <c r="AN14" s="5" t="s">
         <v>226</v>
@@ -11070,67 +11070,65 @@
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>365</v>
+        <v>386</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>390</v>
       </c>
       <c r="C2" s="3">
-        <v>46113</v>
+        <v>46220</v>
       </c>
       <c r="D2" s="4">
-        <v>571606148</v>
+        <v>553063753</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="F2" s="6">
-        <v>46091</v>
+        <v>46099</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="K2" s="3">
-        <v>46278</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="K2" s="3"/>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L13" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
-        <v>156</v>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
+        <v>-111</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
-        <v>178</v>
+        <f ca="1">IF($F2="","",$F2+90-TODAY())</f>
+        <v>-111</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
-        <v>-67</v>
+        <f ca="1">IF($C2="","",$C2+540-TODAY())</f>
+        <v>460</v>
       </c>
       <c r="O2" s="6">
-        <v>46456</v>
+        <v>46189</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>67</v>
+        <v>393</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>47</v>
@@ -11142,7 +11140,7 @@
         <v>48</v>
       </c>
       <c r="Z2" s="7">
-        <v>1294.23</v>
+        <v>3822.49</v>
       </c>
       <c r="AA2" s="7">
         <v>0</v>
@@ -11151,33 +11149,35 @@
         <v>0</v>
       </c>
       <c r="AC2" s="6">
-        <v>46113</v>
+        <v>46220</v>
       </c>
       <c r="AD2" s="7">
-        <v>1294.23</v>
+        <v>3822.49</v>
       </c>
       <c r="AE2" s="4">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="AG2" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI2" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="AH2" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="AI2" s="5"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="5" t="s">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="AL2" s="5" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="AM2" s="6">
-        <v>46106</v>
+        <v>46125</v>
       </c>
       <c r="AN2" s="5" t="s">
         <v>276</v>
@@ -11191,16 +11191,16 @@
         <v>365</v>
       </c>
       <c r="C3" s="3">
-        <v>46126</v>
+        <v>46113</v>
       </c>
       <c r="D3" s="4">
-        <v>571606263</v>
+        <v>571606148</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F3" s="6">
-        <v>46112</v>
+        <v>46091</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>64</v>
@@ -11209,28 +11209,28 @@
         <v>64</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="K3" s="3">
         <v>46278</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>177</v>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
+        <v>156</v>
       </c>
       <c r="M3" s="12">
         <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="N3" s="12">
         <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
-        <v>-54</v>
+        <v>-67</v>
       </c>
       <c r="O3" s="6">
-        <v>46477</v>
+        <v>46456</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>57</v>
@@ -11257,7 +11257,7 @@
         <v>48</v>
       </c>
       <c r="Z3" s="7">
-        <v>2173.29</v>
+        <v>1294.23</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
@@ -11266,22 +11266,22 @@
         <v>0</v>
       </c>
       <c r="AC3" s="6">
-        <v>46126</v>
+        <v>46113</v>
       </c>
       <c r="AD3" s="7">
-        <v>2173.29</v>
+        <v>1294.23</v>
       </c>
       <c r="AE3" s="4">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AG3" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AH3" s="5" t="s">
-        <v>280</v>
+        <v>213</v>
       </c>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="4"/>
@@ -11292,7 +11292,7 @@
         <v>60</v>
       </c>
       <c r="AM3" s="6">
-        <v>46121</v>
+        <v>46106</v>
       </c>
       <c r="AN3" s="5" t="s">
         <v>276</v>
@@ -11302,29 +11302,29 @@
       <c r="A4" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>366</v>
+      <c r="B4" s="2" t="s">
+        <v>365</v>
       </c>
       <c r="C4" s="3">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="D4" s="4">
-        <v>571606836</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>288</v>
+        <v>571606263</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="F4" s="6">
-        <v>46084</v>
+        <v>46112</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>289</v>
+        <v>64</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>289</v>
+        <v>64</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>282</v>
@@ -11333,34 +11333,34 @@
         <v>46278</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-126</v>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
+        <v>177</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
-        <v>-126</v>
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <v>191</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
-        <v>-7</v>
+        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <v>-54</v>
       </c>
       <c r="O4" s="6">
-        <v>46174</v>
+        <v>46477</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>254</v>
+        <v>66</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>47</v>
@@ -11381,26 +11381,24 @@
         <v>0</v>
       </c>
       <c r="AC4" s="6">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="AD4" s="7">
         <v>2173.29</v>
       </c>
       <c r="AE4" s="4">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>158</v>
+        <v>283</v>
       </c>
       <c r="AG4" s="5" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="AH4" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="AI4" s="5" t="s">
-        <v>286</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="AI4" s="5"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
         <v>84</v>
@@ -11409,7 +11407,7 @@
         <v>60</v>
       </c>
       <c r="AM4" s="6">
-        <v>46106</v>
+        <v>46121</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>276</v>
@@ -11420,64 +11418,64 @@
         <v>200</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C5" s="3">
-        <v>46135</v>
+        <v>46113</v>
       </c>
       <c r="D5" s="4">
-        <v>571607238</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>292</v>
+        <v>571606836</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>288</v>
       </c>
       <c r="F5" s="6">
-        <v>46098</v>
+        <v>46084</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>105</v>
+        <v>289</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>105</v>
+        <v>289</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K5" s="3">
         <v>46278</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-112</v>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
+        <v>-126</v>
       </c>
       <c r="M5" s="12">
+        <f ca="1">IF($F5="","",$F5+90-TODAY())</f>
+        <v>-126</v>
+      </c>
+      <c r="N5" s="12">
         <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
-        <v>15</v>
-      </c>
-      <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
-        <v>200</v>
+        <v>-7</v>
       </c>
       <c r="O5" s="6">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>97</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>106</v>
+        <v>254</v>
       </c>
       <c r="R5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T5" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>47</v>
@@ -11489,7 +11487,7 @@
         <v>48</v>
       </c>
       <c r="Z5" s="7">
-        <v>1294.23</v>
+        <v>2173.29</v>
       </c>
       <c r="AA5" s="7">
         <v>0</v>
@@ -11498,22 +11496,26 @@
         <v>0</v>
       </c>
       <c r="AC5" s="6">
-        <v>46135</v>
+        <v>46113</v>
       </c>
       <c r="AD5" s="7">
-        <v>1294.23</v>
+        <v>2173.29</v>
       </c>
       <c r="AE5" s="4">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>293</v>
+        <v>158</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="AH5" s="5"/>
-      <c r="AI5" s="5"/>
+        <v>290</v>
+      </c>
+      <c r="AH5" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="AI5" s="5" t="s">
+        <v>286</v>
+      </c>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
         <v>84</v>
@@ -11522,7 +11524,7 @@
         <v>60</v>
       </c>
       <c r="AM5" s="6">
-        <v>46119</v>
+        <v>46106</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>276</v>
@@ -11530,65 +11532,67 @@
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="C6" s="3">
-        <v>46220</v>
+        <v>46135</v>
       </c>
       <c r="D6" s="4">
-        <v>553063753</v>
+        <v>571607238</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F6" s="6">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="K6" s="3"/>
+        <v>278</v>
+      </c>
+      <c r="K6" s="3">
+        <v>46278</v>
+      </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-111</v>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
+        <v>-112</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
-        <v>-111</v>
+        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <v>15</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+540-TODAY())</f>
-        <v>460</v>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <v>200</v>
       </c>
       <c r="O6" s="6">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>97</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>393</v>
+        <v>57</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>47</v>
@@ -11600,7 +11604,7 @@
         <v>48</v>
       </c>
       <c r="Z6" s="7">
-        <v>3822.49</v>
+        <v>1294.23</v>
       </c>
       <c r="AA6" s="7">
         <v>0</v>
@@ -11609,35 +11613,31 @@
         <v>0</v>
       </c>
       <c r="AC6" s="6">
-        <v>46220</v>
+        <v>46135</v>
       </c>
       <c r="AD6" s="7">
-        <v>3822.49</v>
+        <v>1294.23</v>
       </c>
       <c r="AE6" s="4">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="AH6" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI6" s="5" t="s">
-        <v>280</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="AM6" s="6">
-        <v>46125</v>
+        <v>46119</v>
       </c>
       <c r="AN6" s="5" t="s">
         <v>276</v>
@@ -11678,7 +11678,7 @@
         <v>46278</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v>-111</v>
       </c>
       <c r="M7" s="12">
@@ -11758,28 +11758,28 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C8" s="3">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="D8" s="4">
-        <v>569508762</v>
+        <v>571608266</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F8" s="6">
         <v>46105</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>289</v>
+        <v>101</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>289</v>
+        <v>101</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>42</v>
@@ -11788,19 +11788,19 @@
         <v>278</v>
       </c>
       <c r="K8" s="3">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>-105</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($F8="","",$F8+90-TODAY())</f>
-        <v>-105</v>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v>191</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
-        <v>7</v>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v>191</v>
       </c>
       <c r="O8" s="6">
         <v>46195</v>
@@ -11809,16 +11809,16 @@
         <v>97</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>254</v>
+        <v>102</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>47</v>
@@ -11838,7 +11838,9 @@
       <c r="AB8" s="7">
         <v>0</v>
       </c>
-      <c r="AC8" s="6"/>
+      <c r="AC8" s="6">
+        <v>46126</v>
+      </c>
       <c r="AD8" s="7">
         <v>1294.23</v>
       </c>
@@ -11846,13 +11848,13 @@
         <v>137</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="AG8" s="5" t="s">
-        <v>280</v>
+        <v>166</v>
       </c>
       <c r="AH8" s="5" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4"/>
@@ -11873,65 +11875,65 @@
       <c r="A9" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>370</v>
+      <c r="B9" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="C9" s="3">
-        <v>46126</v>
-      </c>
-      <c r="D9" s="4">
-        <v>571608266</v>
+        <v>46113</v>
+      </c>
+      <c r="D9" s="14">
+        <v>553787632</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F9" s="6">
-        <v>46105</v>
+        <v>46085</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>101</v>
+        <v>307</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>101</v>
+        <v>307</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>278</v>
+      <c r="J9" s="15" t="s">
+        <v>371</v>
       </c>
       <c r="K9" s="3">
-        <v>46278</v>
+        <v>46282</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-105</v>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
+        <v>-95</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>191</v>
+        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
+        <v>-7</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>191</v>
+        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
+        <v>-7</v>
       </c>
       <c r="O9" s="6">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="S9" s="5" t="s">
         <v>47</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>47</v>
@@ -11943,7 +11945,7 @@
         <v>48</v>
       </c>
       <c r="Z9" s="7">
-        <v>1294.23</v>
+        <v>2943.43</v>
       </c>
       <c r="AA9" s="7">
         <v>0</v>
@@ -11952,33 +11954,31 @@
         <v>0</v>
       </c>
       <c r="AC9" s="6">
-        <v>46126</v>
+        <v>46113</v>
       </c>
       <c r="AD9" s="7">
-        <v>1294.23</v>
+        <v>2943.43</v>
       </c>
       <c r="AE9" s="4">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>213</v>
+        <v>301</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="AH9" s="5" t="s">
-        <v>285</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>60</v>
+        <v>302</v>
       </c>
       <c r="AM9" s="6">
-        <v>46121</v>
+        <v>46106</v>
       </c>
       <c r="AN9" s="5" t="s">
         <v>276</v>
@@ -11989,64 +11989,64 @@
         <v>200</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="C10" s="3">
-        <v>46113</v>
-      </c>
-      <c r="D10" s="14">
-        <v>553787632</v>
+        <v>46146</v>
+      </c>
+      <c r="D10" s="4">
+        <v>571612561</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F10" s="6">
-        <v>46085</v>
+        <v>46098</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="15" t="s">
-        <v>371</v>
-      </c>
-      <c r="K10" s="3">
-        <v>46282</v>
+      <c r="J10" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="K10" s="16">
+        <v>46278</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-95</v>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
+        <v>-112</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" ref="M10:N12" ca="1" si="1">IF($C10="","",$C10+180-TODAY())</f>
-        <v>-7</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>211</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>-7</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>211</v>
       </c>
       <c r="O10" s="6">
-        <v>46205</v>
+        <v>46188</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>275</v>
+        <v>314</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="S10" s="5" t="s">
         <v>47</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="U10" s="5" t="s">
         <v>47</v>
@@ -12058,7 +12058,7 @@
         <v>48</v>
       </c>
       <c r="Z10" s="7">
-        <v>2943.43</v>
+        <v>3822.49</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -12067,28 +12067,30 @@
         <v>0</v>
       </c>
       <c r="AC10" s="6">
-        <v>46113</v>
+        <v>46146</v>
       </c>
       <c r="AD10" s="7">
-        <v>2943.43</v>
+        <v>3822.49</v>
       </c>
       <c r="AE10" s="4">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="AG10" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="AH10" s="5"/>
+        <v>316</v>
+      </c>
+      <c r="AH10" s="5" t="s">
+        <v>290</v>
+      </c>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>302</v>
+        <v>60</v>
       </c>
       <c r="AM10" s="6">
         <v>46106</v>
@@ -12102,61 +12104,61 @@
         <v>61</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C11" s="3">
-        <v>46129</v>
+        <v>46127</v>
       </c>
       <c r="D11" s="4">
-        <v>553810379</v>
+        <v>569508762</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F11" s="6">
-        <v>46092</v>
+        <v>46105</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="K11" s="16">
-        <v>46278</v>
+        <v>278</v>
+      </c>
+      <c r="K11" s="3">
+        <v>46269</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-88</v>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
+        <v>-105</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <f ca="1">IF($F11="","",$F11+90-TODAY())</f>
+        <v>-105</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
+        <v>7</v>
       </c>
       <c r="O11" s="6">
-        <v>46212</v>
+        <v>46195</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>133</v>
+        <v>254</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T11" s="5" t="s">
         <v>44</v>
@@ -12171,7 +12173,7 @@
         <v>48</v>
       </c>
       <c r="Z11" s="7">
-        <v>879.06</v>
+        <v>1294.23</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -12179,32 +12181,32 @@
       <c r="AB11" s="7">
         <v>0</v>
       </c>
-      <c r="AC11" s="6">
-        <v>46129</v>
-      </c>
+      <c r="AC11" s="6"/>
       <c r="AD11" s="7">
-        <v>879.06</v>
+        <v>1294.23</v>
       </c>
       <c r="AE11" s="4">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>301</v>
+        <v>151</v>
       </c>
       <c r="AG11" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="AH11" s="5"/>
+        <v>280</v>
+      </c>
+      <c r="AH11" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>302</v>
+        <v>60</v>
       </c>
       <c r="AM11" s="6">
-        <v>46106</v>
+        <v>46121</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>276</v>
@@ -12218,22 +12220,22 @@
         <v>372</v>
       </c>
       <c r="C12" s="3">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="D12" s="4">
-        <v>555438747</v>
+        <v>553810379</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F12" s="6">
-        <v>46112</v>
+        <v>46092</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>42</v>
@@ -12245,25 +12247,25 @@
         <v>46278</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-68</v>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
+        <v>-88</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <v>9</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <v>9</v>
       </c>
       <c r="O12" s="6">
-        <v>46232</v>
+        <v>46212</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>67</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>275</v>
+        <v>133</v>
       </c>
       <c r="R12" s="5" t="s">
         <v>44</v>
@@ -12293,31 +12295,31 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="AD12" s="7">
         <v>879.06</v>
       </c>
       <c r="AE12" s="4">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AF12" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AG12" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="AG12" s="5" t="s">
-        <v>280</v>
       </c>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>60</v>
+        <v>302</v>
       </c>
       <c r="AM12" s="6">
-        <v>46121</v>
+        <v>46106</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>276</v>
@@ -12325,67 +12327,67 @@
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>373</v>
+        <v>61</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>372</v>
       </c>
       <c r="C13" s="3">
-        <v>46146</v>
+        <v>46127</v>
       </c>
       <c r="D13" s="4">
-        <v>571612561</v>
+        <v>555438747</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F13" s="6">
-        <v>46098</v>
+        <v>46112</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="K13" s="16">
         <v>46278</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-112</v>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
+        <v>-68</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v>211</v>
+        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <v>7</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v>211</v>
+        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <v>7</v>
       </c>
       <c r="O13" s="6">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="S13" s="5" t="s">
         <v>47</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>47</v>
@@ -12397,7 +12399,7 @@
         <v>48</v>
       </c>
       <c r="Z13" s="7">
-        <v>3822.49</v>
+        <v>879.06</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -12406,23 +12408,21 @@
         <v>0</v>
       </c>
       <c r="AC13" s="6">
-        <v>46146</v>
+        <v>46127</v>
       </c>
       <c r="AD13" s="7">
-        <v>3822.49</v>
+        <v>879.06</v>
       </c>
       <c r="AE13" s="4">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="AG13" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH13" s="5" t="s">
-        <v>290</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
@@ -12432,7 +12432,7 @@
         <v>60</v>
       </c>
       <c r="AM13" s="6">
-        <v>46106</v>
+        <v>46121</v>
       </c>
       <c r="AN13" s="5" t="s">
         <v>276</v>
@@ -12576,7 +12576,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>395</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>323</v>
       </c>

--- a/SPC26S1 - 03 March.xlsx
+++ b/SPC26S1 - 03 March.xlsx
@@ -2195,7 +2195,7 @@
     <t>66 claims with a date of service in 2026-03 March, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
-    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim goes to the bottom even when its Latest Date Worked is empty). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the top group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
     <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
@@ -9436,79 +9436,79 @@
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>200</v>
+        <v>342</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>374</v>
+        <v>343</v>
       </c>
       <c r="C3" s="3">
-        <v>46107</v>
+        <v>46203</v>
       </c>
       <c r="D3" s="4">
-        <v>553613990</v>
+        <v>553643849</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="F3" s="6">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="K3" s="3">
-        <v>46279</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="K3" s="3"/>
       <c r="L3" s="12">
         <f ca="1">IF($O3="","",$O3-TODAY())</f>
-        <v>148</v>
+        <v>-123</v>
       </c>
       <c r="M3" s="12">
+        <f ca="1">IF($F3="","",$F3+90-TODAY())</f>
+        <v>-123</v>
+      </c>
+      <c r="N3" s="12">
         <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v>172</v>
-      </c>
-      <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
-        <v>-73</v>
+        <v>268</v>
       </c>
       <c r="O3" s="6">
-        <v>46448</v>
+        <v>46177</v>
       </c>
       <c r="P3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V3" s="5"/>
+      <c r="V3" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
       <c r="Y3" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z3" s="7">
-        <v>5784.24</v>
+        <v>18400.34</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
@@ -9516,32 +9516,30 @@
       <c r="AB3" s="7">
         <v>0</v>
       </c>
-      <c r="AC3" s="6">
-        <v>46107</v>
-      </c>
+      <c r="AC3" s="6"/>
       <c r="AD3" s="7">
-        <v>5784.24</v>
+        <v>18400.34</v>
       </c>
       <c r="AE3" s="4">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>167</v>
+        <v>261</v>
       </c>
       <c r="AG3" s="5" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="AH3" s="5"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="5" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="AM3" s="6">
-        <v>46105</v>
+        <v>46197</v>
       </c>
       <c r="AN3" s="5" t="s">
         <v>226</v>
@@ -9551,20 +9549,20 @@
       <c r="A4" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>376</v>
+      <c r="B4" s="2" t="s">
+        <v>374</v>
       </c>
       <c r="C4" s="3">
-        <v>46203</v>
+        <v>46107</v>
       </c>
       <c r="D4" s="4">
-        <v>552282896</v>
+        <v>553613990</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F4" s="6">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>64</v>
@@ -9573,28 +9571,28 @@
         <v>64</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K4" s="3">
         <v>46279</v>
       </c>
       <c r="L4" s="12">
         <f ca="1">IF($O4="","",$O4-TODAY())</f>
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M4" s="12">
         <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
-        <v>268</v>
+        <v>172</v>
       </c>
       <c r="N4" s="12">
         <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
-        <v>23</v>
+        <v>-73</v>
       </c>
       <c r="O4" s="6">
-        <v>46450</v>
+        <v>46448</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>57</v>
@@ -9621,7 +9619,7 @@
         <v>48</v>
       </c>
       <c r="Z4" s="7">
-        <v>9056.39</v>
+        <v>5784.24</v>
       </c>
       <c r="AA4" s="7">
         <v>0</v>
@@ -9630,35 +9628,31 @@
         <v>0</v>
       </c>
       <c r="AC4" s="6">
-        <v>46203</v>
+        <v>46107</v>
       </c>
       <c r="AD4" s="7">
-        <v>9056.39</v>
+        <v>5784.24</v>
       </c>
       <c r="AE4" s="4">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="AG4" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="AH4" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="AI4" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AL4" s="5" t="s">
         <v>211</v>
       </c>
       <c r="AM4" s="6">
-        <v>46197</v>
+        <v>46105</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>226</v>
@@ -9666,22 +9660,22 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>375</v>
+        <v>200</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>376</v>
       </c>
       <c r="C5" s="3">
-        <v>46108</v>
+        <v>46203</v>
       </c>
       <c r="D5" s="4">
-        <v>553223068</v>
+        <v>552282896</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="F5" s="6">
-        <v>46099</v>
+        <v>46085</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>64</v>
@@ -9693,25 +9687,25 @@
         <v>70</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="K5" s="3">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="L5" s="12">
         <f ca="1">IF($O5="","",$O5-TODAY())</f>
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="M5" s="12">
         <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
-        <v>173</v>
+        <v>268</v>
       </c>
       <c r="N5" s="12">
         <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
-        <v>-72</v>
+        <v>23</v>
       </c>
       <c r="O5" s="6">
-        <v>46464</v>
+        <v>46450</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>57</v>
@@ -9738,7 +9732,7 @@
         <v>48</v>
       </c>
       <c r="Z5" s="7">
-        <v>2493.33</v>
+        <v>9056.39</v>
       </c>
       <c r="AA5" s="7">
         <v>0</v>
@@ -9747,31 +9741,35 @@
         <v>0</v>
       </c>
       <c r="AC5" s="6">
-        <v>46108</v>
+        <v>46203</v>
       </c>
       <c r="AD5" s="7">
-        <v>2493.33</v>
+        <v>9056.39</v>
       </c>
       <c r="AE5" s="4">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="AH5" s="5"/>
-      <c r="AI5" s="5"/>
+        <v>230</v>
+      </c>
+      <c r="AH5" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="AI5" s="5" t="s">
+        <v>232</v>
+      </c>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="AM5" s="6">
-        <v>46101</v>
+        <v>46197</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>226</v>
@@ -9779,22 +9777,22 @@
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>200</v>
+        <v>354</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C6" s="3">
-        <v>46203</v>
+        <v>46108</v>
       </c>
       <c r="D6" s="4">
-        <v>555372244</v>
+        <v>553223068</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F6" s="6">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>64</v>
@@ -9806,25 +9804,25 @@
         <v>70</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="K6" s="3">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="L6" s="12">
         <f ca="1">IF($O6="","",$O6-TODAY())</f>
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M6" s="12">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>268</v>
+        <v>173</v>
       </c>
       <c r="N6" s="12">
         <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
-        <v>23</v>
+        <v>-72</v>
       </c>
       <c r="O6" s="6">
-        <v>46469</v>
+        <v>46464</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>57</v>
@@ -9844,16 +9842,14 @@
       <c r="U6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V6" s="5" t="s">
-        <v>242</v>
-      </c>
+      <c r="V6" s="5"/>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z6" s="7">
-        <v>19949.23</v>
+        <v>2493.33</v>
       </c>
       <c r="AA6" s="7">
         <v>0</v>
@@ -9862,35 +9858,31 @@
         <v>0</v>
       </c>
       <c r="AC6" s="6">
-        <v>46203</v>
+        <v>46108</v>
       </c>
       <c r="AD6" s="7">
-        <v>19949.23</v>
+        <v>2493.33</v>
       </c>
       <c r="AE6" s="4">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="AH6" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI6" s="5" t="s">
-        <v>158</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="AM6" s="6">
-        <v>46197</v>
+        <v>46101</v>
       </c>
       <c r="AN6" s="5" t="s">
         <v>226</v>
@@ -9898,52 +9890,52 @@
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>354</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C7" s="3">
-        <v>46122</v>
+        <v>46203</v>
       </c>
       <c r="D7" s="4">
-        <v>553825634</v>
+        <v>555372244</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F7" s="6">
-        <v>46106</v>
+        <v>46104</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>64</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="K7" s="3">
         <v>46279</v>
       </c>
       <c r="L7" s="12">
         <f ca="1">IF($O7="","",$O7-TODAY())</f>
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M7" s="12">
         <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>187</v>
+        <v>268</v>
       </c>
       <c r="N7" s="12">
         <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
-        <v>-58</v>
+        <v>23</v>
       </c>
       <c r="O7" s="6">
-        <v>46471</v>
+        <v>46469</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>57</v>
@@ -9963,47 +9955,53 @@
       <c r="U7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V7" s="5"/>
+      <c r="V7" s="5" t="s">
+        <v>242</v>
+      </c>
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z7" s="7">
-        <v>2493.33</v>
+        <v>19949.23</v>
       </c>
       <c r="AA7" s="7">
-        <v>2351.73</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="7">
-        <v>110.6</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="6">
-        <v>46122</v>
+        <v>46203</v>
       </c>
       <c r="AD7" s="7">
-        <v>31</v>
+        <v>19949.23</v>
       </c>
       <c r="AE7" s="4">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="AG7" s="5"/>
-      <c r="AH7" s="5"/>
-      <c r="AI7" s="5"/>
-      <c r="AJ7" s="4">
-        <v>557571095</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="AG7" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="AH7" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI7" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
-        <v>84</v>
+        <v>233</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="AM7" s="6">
-        <v>46107</v>
+        <v>46197</v>
       </c>
       <c r="AN7" s="5" t="s">
         <v>226</v>
@@ -10017,46 +10015,46 @@
         <v>378</v>
       </c>
       <c r="C8" s="3">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="D8" s="4">
-        <v>554186385</v>
+        <v>553825634</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F8" s="6">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>248</v>
+        <v>86</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>64</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>248</v>
+        <v>86</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="K8" s="3">
         <v>46279</v>
       </c>
       <c r="L8" s="12">
         <f ca="1">IF($O8="","",$O8-TODAY())</f>
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M8" s="12">
         <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N8" s="12">
         <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
-        <v>-54</v>
+        <v>-58</v>
       </c>
       <c r="O8" s="6">
-        <v>46473</v>
+        <v>46471</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>57</v>
@@ -10076,49 +10074,47 @@
       <c r="U8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V8" s="5" t="s">
-        <v>221</v>
-      </c>
+      <c r="V8" s="5"/>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z8" s="7">
-        <v>5614.63</v>
+        <v>2493.33</v>
       </c>
       <c r="AA8" s="7">
-        <v>4889.05</v>
+        <v>2351.73</v>
       </c>
       <c r="AB8" s="7">
-        <v>578.1</v>
+        <v>110.6</v>
       </c>
       <c r="AC8" s="6">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="AD8" s="7">
-        <v>147.47999999999999</v>
+        <v>31</v>
       </c>
       <c r="AE8" s="4">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AG8" s="5"/>
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4">
-        <v>557570916</v>
+        <v>557571095</v>
       </c>
       <c r="AK8" s="5" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="AM8" s="6">
-        <v>46112</v>
+        <v>46107</v>
       </c>
       <c r="AN8" s="5" t="s">
         <v>226</v>
@@ -10126,102 +10122,106 @@
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>200</v>
+        <v>354</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C9" s="3">
-        <v>46097</v>
+        <v>46126</v>
       </c>
       <c r="D9" s="4">
-        <v>551964467</v>
+        <v>554186385</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="F9" s="6">
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>125</v>
+        <v>248</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>42</v>
+        <v>248</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="K9" s="3">
         <v>46279</v>
       </c>
       <c r="L9" s="12">
         <f ca="1">IF($O9="","",$O9-TODAY())</f>
-        <v>-123</v>
+        <v>173</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
-        <v>-123</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>191</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+540-TODAY())</f>
-        <v>337</v>
+        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <v>-54</v>
       </c>
       <c r="O9" s="6">
-        <v>46177</v>
+        <v>46473</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>393</v>
+        <v>67</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V9" s="5"/>
+      <c r="V9" s="5" t="s">
+        <v>221</v>
+      </c>
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z9" s="7">
-        <v>7623.07</v>
+        <v>5614.63</v>
       </c>
       <c r="AA9" s="7">
-        <v>0</v>
+        <v>4889.05</v>
       </c>
       <c r="AB9" s="7">
-        <v>0</v>
+        <v>578.1</v>
       </c>
       <c r="AC9" s="6">
-        <v>46097</v>
+        <v>46126</v>
       </c>
       <c r="AD9" s="7">
-        <v>7623.07</v>
+        <v>147.47999999999999</v>
       </c>
       <c r="AE9" s="4">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>159</v>
+        <v>250</v>
       </c>
       <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
-      <c r="AJ9" s="4"/>
+      <c r="AJ9" s="4">
+        <v>557570916</v>
+      </c>
       <c r="AK9" s="5" t="s">
         <v>119</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>211</v>
       </c>
       <c r="AM9" s="6">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c r="AN9" s="5" t="s">
         <v>226</v>
@@ -10240,19 +10240,19 @@
         <v>200</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C10" s="3">
-        <v>46108</v>
+        <v>46097</v>
       </c>
       <c r="D10" s="4">
-        <v>553652690</v>
+        <v>551964467</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="F10" s="6">
-        <v>46093</v>
+        <v>46087</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>125</v>
@@ -10264,25 +10264,25 @@
         <v>42</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="K10" s="3">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="L10" s="12">
         <f ca="1">IF($O10="","",$O10-TODAY())</f>
-        <v>-117</v>
+        <v>-123</v>
       </c>
       <c r="M10" s="12">
         <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
-        <v>-117</v>
+        <v>-123</v>
       </c>
       <c r="N10" s="12">
         <f ca="1">IF($C10="","",$C10+540-TODAY())</f>
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="O10" s="6">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>97</v>
@@ -10302,16 +10302,14 @@
       <c r="U10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V10" s="5" t="s">
-        <v>260</v>
-      </c>
+      <c r="V10" s="5"/>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z10" s="7">
-        <v>18400.34</v>
+        <v>7623.07</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -10320,31 +10318,29 @@
         <v>0</v>
       </c>
       <c r="AC10" s="6">
-        <v>46108</v>
+        <v>46097</v>
       </c>
       <c r="AD10" s="7">
-        <v>18400.34</v>
+        <v>7623.07</v>
       </c>
       <c r="AE10" s="4">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>267</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="AG10" s="5"/>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>263</v>
+        <v>119</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="AM10" s="6">
-        <v>46105</v>
+        <v>46091</v>
       </c>
       <c r="AN10" s="5" t="s">
         <v>226</v>
@@ -10355,16 +10351,16 @@
         <v>200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C11" s="3">
-        <v>46220</v>
+        <v>46108</v>
       </c>
       <c r="D11" s="4">
-        <v>553656838</v>
+        <v>553652690</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F11" s="6">
         <v>46093</v>
@@ -10379,10 +10375,10 @@
         <v>42</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K11" s="3">
-        <v>46279</v>
+        <v>46265</v>
       </c>
       <c r="L11" s="12">
         <f ca="1">IF($O11="","",$O11-TODAY())</f>
@@ -10394,7 +10390,7 @@
       </c>
       <c r="N11" s="12">
         <f ca="1">IF($C11="","",$C11+540-TODAY())</f>
-        <v>460</v>
+        <v>348</v>
       </c>
       <c r="O11" s="6">
         <v>46183</v>
@@ -10417,14 +10413,16 @@
       <c r="U11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V11" s="5"/>
+      <c r="V11" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z11" s="7">
-        <v>12650.96</v>
+        <v>18400.34</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -10433,10 +10431,10 @@
         <v>0</v>
       </c>
       <c r="AC11" s="6">
-        <v>46220</v>
+        <v>46108</v>
       </c>
       <c r="AD11" s="7">
-        <v>12650.96</v>
+        <v>18400.34</v>
       </c>
       <c r="AE11" s="4">
         <v>149</v>
@@ -10445,7 +10443,7 @@
         <v>158</v>
       </c>
       <c r="AG11" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
@@ -10468,31 +10466,31 @@
         <v>200</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C12" s="3">
-        <v>46127</v>
+        <v>46220</v>
       </c>
       <c r="D12" s="4">
-        <v>555351211</v>
+        <v>553656838</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F12" s="6">
         <v>46093</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="K12" s="3">
         <v>46279</v>
@@ -10502,12 +10500,12 @@
         <v>-117</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
-        <v>7</v>
+        <f ca="1">IF($F12="","",$F12+90-TODAY())</f>
+        <v>-117</v>
       </c>
       <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>192</v>
+        <f ca="1">IF($C12="","",$C12+540-TODAY())</f>
+        <v>460</v>
       </c>
       <c r="O12" s="6">
         <v>46183</v>
@@ -10516,16 +10514,16 @@
         <v>97</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>57</v>
+        <v>393</v>
       </c>
       <c r="U12" s="5" t="s">
         <v>47</v>
@@ -10537,7 +10535,7 @@
         <v>48</v>
       </c>
       <c r="Z12" s="7">
-        <v>8277.57</v>
+        <v>12650.96</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -10546,31 +10544,31 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46127</v>
+        <v>46220</v>
       </c>
       <c r="AD12" s="7">
-        <v>8277.57</v>
+        <v>12650.96</v>
       </c>
       <c r="AE12" s="4">
         <v>149</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AG12" s="5" t="s">
-        <v>158</v>
+        <v>270</v>
       </c>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="AM12" s="6">
-        <v>46120</v>
+        <v>46105</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>226</v>
@@ -10578,58 +10576,58 @@
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>354</v>
+        <v>200</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C13" s="3">
-        <v>46163</v>
+        <v>46127</v>
       </c>
       <c r="D13" s="4">
-        <v>553378154</v>
+        <v>555351211</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F13" s="6">
-        <v>46101</v>
+        <v>46093</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>274</v>
+        <v>104</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>274</v>
+        <v>104</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="K13" s="3">
-        <v>46268</v>
+        <v>46279</v>
       </c>
       <c r="L13" s="12">
         <f ca="1">IF($O13="","",$O13-TODAY())</f>
-        <v>-79</v>
+        <v>-117</v>
       </c>
       <c r="M13" s="12">
         <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
-        <v>43</v>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>192</v>
       </c>
       <c r="O13" s="6">
-        <v>46221</v>
+        <v>46183</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>275</v>
+        <v>111</v>
       </c>
       <c r="R13" s="5" t="s">
         <v>44</v>
@@ -10638,7 +10636,7 @@
         <v>47</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>47</v>
@@ -10650,7 +10648,7 @@
         <v>48</v>
       </c>
       <c r="Z13" s="7">
-        <v>7623.07</v>
+        <v>8277.57</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -10659,29 +10657,31 @@
         <v>0</v>
       </c>
       <c r="AC13" s="6">
-        <v>46163</v>
+        <v>46127</v>
       </c>
       <c r="AD13" s="7">
-        <v>7623.07</v>
+        <v>8277.57</v>
       </c>
       <c r="AE13" s="4">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="AG13" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="AG13" s="5" t="s">
+        <v>158</v>
+      </c>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="AM13" s="6">
-        <v>46105</v>
+        <v>46120</v>
       </c>
       <c r="AN13" s="5" t="s">
         <v>226</v>
@@ -10689,79 +10689,79 @@
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>343</v>
+        <v>383</v>
       </c>
       <c r="C14" s="3">
-        <v>46203</v>
+        <v>46163</v>
       </c>
       <c r="D14" s="4">
-        <v>553643849</v>
+        <v>553378154</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="F14" s="6">
-        <v>46087</v>
+        <v>46101</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>70</v>
+        <v>274</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>70</v>
+        <v>274</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>42</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="K14" s="3"/>
+        <v>257</v>
+      </c>
+      <c r="K14" s="3">
+        <v>46268</v>
+      </c>
       <c r="L14" s="12">
         <f ca="1">IF($O14="","",$O14-TODAY())</f>
-        <v>-123</v>
+        <v>-79</v>
       </c>
       <c r="M14" s="12">
-        <f ca="1">IF($F14="","",$F14+90-TODAY())</f>
-        <v>-123</v>
+        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <v>43</v>
       </c>
       <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
-        <v>268</v>
+        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <v>43</v>
       </c>
       <c r="O14" s="6">
-        <v>46177</v>
+        <v>46221</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>98</v>
+        <v>275</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="U14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V14" s="5" t="s">
-        <v>260</v>
-      </c>
+      <c r="V14" s="5"/>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Z14" s="7">
-        <v>18400.34</v>
+        <v>7623.07</v>
       </c>
       <c r="AA14" s="7">
         <v>0</v>
@@ -10769,30 +10769,30 @@
       <c r="AB14" s="7">
         <v>0</v>
       </c>
-      <c r="AC14" s="6"/>
+      <c r="AC14" s="6">
+        <v>46163</v>
+      </c>
       <c r="AD14" s="7">
-        <v>18400.34</v>
+        <v>7623.07</v>
       </c>
       <c r="AE14" s="4">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="AG14" s="5" t="s">
-        <v>262</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="AG14" s="5"/>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="AM14" s="6">
-        <v>46197</v>
+        <v>46105</v>
       </c>
       <c r="AN14" s="5" t="s">
         <v>226</v>

--- a/SPC26S1 - 03 March.xlsx
+++ b/SPC26S1 - 03 March.xlsx
@@ -1979,7 +1979,7 @@
     <t>Past due rows sit below the claims that can still be filed on time rather than at the very top, so the actionable work stays first. That is why the numbers run up to the longest window and then restart at the negatives.</t>
   </si>
   <si>
-    <t>Filing Deadline is the date of service plus the primary payer's limit, taken from 'Carrier_Timely_Filing_Reference.xlsx'. Days Until Deadline is a live formula, so the count stays true as time passes - but the row order is a snapshot taken on 12 August 2026. Sorting on Days Until Deadline alone would mix the three groups above back together, so when you re-sort keep the empty Latest Date Worked rows first and the Finalized and PAID rows last.</t>
+    <t>Filing Deadline is the date of service plus the primary payer's limit, taken from 'Carrier_Timely_Filing_Reference.xlsx'. Days Until Deadline is a live formula, so the count stays true as time passes - but the row order is a snapshot taken on 12 August 2026. Sorting on Days Until Deadline alone would mix the four groups above back together, so when you re-sort keep the Rejected rows first, then the empty Latest Date Worked rows, and the Finalized and PAID rows last.</t>
   </si>
   <si>
     <t>Where a payer had two possible limits the shorter one was used, so the real deadline can only be later, never earlier. Filing Limit and Limit Carrier name the figure applied and the carrier row it came from.</t>
@@ -2195,7 +2195,7 @@
     <t>66 claims with a date of service in 2026-03 March, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
-    <t>Every specialty sheet is sorted in three groups: claims with an empty Latest Date Worked (column K) at the top, then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the top group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+    <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
     <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
@@ -12576,7 +12576,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>395</v>
       </c>

--- a/SPC26S1 - 03 March.xlsx
+++ b/SPC26S1 - 03 March.xlsx
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BH!$A$1:$AO$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DME!$A$1:$AO$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DME!$A$1:$AO$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">GAE!$A$1:$AO$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ORTHO!$A$1:$AO$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">US!$A$1:$AO$13</definedName>
@@ -2192,7 +2192,7 @@
     <t>540 days</t>
   </si>
   <si>
-    <t>66 claims with a date of service in 2026-03 March, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
+    <t>64 claims with a date of service in 2026-03 March, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
   </si>
   <si>
     <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
@@ -2201,13 +2201,13 @@
     <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
   </si>
   <si>
-    <t xml:space="preserve">    3 - Due in 31+ days: 23</t>
+    <t xml:space="preserve">    3 - Due in 31+ days: 21</t>
   </si>
   <si>
     <t xml:space="preserve">    5 - No limit on file: 3</t>
   </si>
   <si>
-    <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+    <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 477 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
   <si>
     <t>Uploaded MR - PIQ-92059096</t>
@@ -7234,7 +7234,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7865,49 +7865,49 @@
         <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>342</v>
+        <v>403</v>
       </c>
       <c r="C6" s="3">
-        <v>46249</v>
+        <v>46156</v>
       </c>
       <c r="D6" s="4">
-        <v>557717115</v>
+        <v>556757813</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F6" s="6">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="K6" s="3">
-        <v>46261</v>
+        <v>46300</v>
       </c>
       <c r="L6" s="12">
         <f ca="1">IF($O6="","",$O6-TODAY())</f>
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="M6" s="12">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>314</v>
+        <v>221</v>
       </c>
       <c r="N6" s="12">
         <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
-        <v>69</v>
+        <v>-24</v>
       </c>
       <c r="O6" s="6">
-        <v>46462</v>
+        <v>46469</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>57</v>
@@ -7928,48 +7928,48 @@
         <v>47</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="Z6" s="7">
-        <v>18176.900000000001</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AA6" s="7">
         <v>0</v>
       </c>
       <c r="AB6" s="7">
-        <v>542.44000000000005</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="6">
-        <v>46165</v>
+        <v>46156</v>
       </c>
       <c r="AD6" s="7">
-        <v>17634.46</v>
+        <v>36353.800000000003</v>
       </c>
       <c r="AE6" s="4">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="AF6" s="5" t="s">
         <v>166</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>168</v>
+        <v>87</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="AM6" s="6">
-        <v>46115</v>
+        <v>46133</v>
       </c>
       <c r="AN6" s="5" t="s">
         <v>154</v>
@@ -7980,49 +7980,49 @@
         <v>61</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C7" s="3">
-        <v>46156</v>
+        <v>46121</v>
       </c>
       <c r="D7" s="4">
-        <v>556757813</v>
+        <v>554941943</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F7" s="6">
-        <v>46104</v>
+        <v>46112</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="K7" s="3">
         <v>46300</v>
       </c>
       <c r="L7" s="12">
         <f ca="1">IF($O7="","",$O7-TODAY())</f>
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="M7" s="12">
         <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="N7" s="12">
         <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
-        <v>-24</v>
+        <v>-59</v>
       </c>
       <c r="O7" s="6">
-        <v>46469</v>
+        <v>46477</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>57</v>
@@ -8043,15 +8043,15 @@
         <v>47</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5" t="s">
-        <v>177</v>
+        <v>48</v>
       </c>
       <c r="Z7" s="7">
-        <v>36353.800000000003</v>
+        <v>6392.96</v>
       </c>
       <c r="AA7" s="7">
         <v>0</v>
@@ -8060,31 +8060,33 @@
         <v>0</v>
       </c>
       <c r="AC7" s="6">
-        <v>46156</v>
+        <v>46121</v>
       </c>
       <c r="AD7" s="7">
-        <v>36353.800000000003</v>
+        <v>6392.96</v>
       </c>
       <c r="AE7" s="4">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="AF7" s="5" t="s">
         <v>166</v>
       </c>
       <c r="AG7" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="AH7" s="5"/>
+        <v>183</v>
+      </c>
+      <c r="AH7" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="AI7" s="5"/>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AM7" s="6">
-        <v>46133</v>
+        <v>46118</v>
       </c>
       <c r="AN7" s="5" t="s">
         <v>154</v>
@@ -8095,55 +8097,55 @@
         <v>61</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C8" s="3">
-        <v>46249</v>
+        <v>46129</v>
       </c>
       <c r="D8" s="4">
-        <v>556761529</v>
+        <v>555728365</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F8" s="6">
-        <v>46111</v>
+        <v>46092</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="K8" s="3">
-        <v>46261</v>
+        <v>46257</v>
       </c>
       <c r="L8" s="12">
         <f ca="1">IF($O8="","",$O8-TODAY())</f>
-        <v>176</v>
+        <v>-118</v>
       </c>
       <c r="M8" s="12">
         <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
-        <v>314</v>
+        <v>194</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
-        <v>69</v>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v>194</v>
       </c>
       <c r="O8" s="6">
-        <v>46476</v>
+        <v>46182</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="R8" s="5" t="s">
         <v>57</v>
@@ -8152,54 +8154,52 @@
         <v>47</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>47</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5" t="s">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="Z8" s="7">
-        <v>18176.900000000001</v>
+        <v>6392.96</v>
       </c>
       <c r="AA8" s="7">
         <v>0</v>
       </c>
       <c r="AB8" s="7">
-        <v>542.44000000000005</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>46154</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC8" s="6"/>
       <c r="AD8" s="7">
-        <v>17634.46</v>
+        <v>6392.96</v>
       </c>
       <c r="AE8" s="4">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="AG8" s="5" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="AM8" s="6">
-        <v>46133</v>
+        <v>46125</v>
       </c>
       <c r="AN8" s="5" t="s">
         <v>154</v>
@@ -8210,55 +8210,55 @@
         <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>404</v>
+        <v>340</v>
       </c>
       <c r="C9" s="3">
-        <v>46121</v>
+        <v>46227</v>
       </c>
       <c r="D9" s="4">
-        <v>554941943</v>
+        <v>552871981</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F9" s="6">
-        <v>46112</v>
+        <v>46097</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>182</v>
+        <v>42</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="K9" s="3">
-        <v>46300</v>
+        <v>46245</v>
       </c>
       <c r="L9" s="12">
         <f ca="1">IF($O9="","",$O9-TODAY())</f>
-        <v>177</v>
+        <v>-113</v>
       </c>
       <c r="M9" s="12">
         <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
-        <v>-59</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>292</v>
       </c>
       <c r="O9" s="6">
-        <v>46477</v>
+        <v>46187</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="R9" s="5" t="s">
         <v>57</v>
@@ -8267,21 +8267,21 @@
         <v>47</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>47</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="5" t="s">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="Z9" s="7">
-        <v>6392.96</v>
+        <v>5916.4</v>
       </c>
       <c r="AA9" s="7">
         <v>0</v>
@@ -8289,270 +8289,40 @@
       <c r="AB9" s="7">
         <v>0</v>
       </c>
-      <c r="AC9" s="6">
-        <v>46121</v>
-      </c>
+      <c r="AC9" s="6"/>
       <c r="AD9" s="7">
-        <v>6392.96</v>
+        <v>5916.4</v>
       </c>
       <c r="AE9" s="4">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="AH9" s="5" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="AM9" s="6">
-        <v>46118</v>
+        <v>46217</v>
       </c>
       <c r="AN9" s="5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C10" s="3">
-        <v>46129</v>
-      </c>
-      <c r="D10" s="4">
-        <v>555728365</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F10" s="6">
-        <v>46092</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="K10" s="3">
-        <v>46257</v>
-      </c>
-      <c r="L10" s="12">
-        <f ca="1">IF($O10="","",$O10-TODAY())</f>
-        <v>-118</v>
-      </c>
-      <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>194</v>
-      </c>
-      <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>194</v>
-      </c>
-      <c r="O10" s="6">
-        <v>46182</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z10" s="7">
-        <v>6392.96</v>
-      </c>
-      <c r="AA10" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="7">
-        <v>6392.96</v>
-      </c>
-      <c r="AE10" s="4">
-        <v>150</v>
-      </c>
-      <c r="AF10" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="AH10" s="5"/>
-      <c r="AI10" s="5"/>
-      <c r="AJ10" s="4"/>
-      <c r="AK10" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL10" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM10" s="6">
-        <v>46125</v>
-      </c>
-      <c r="AN10" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C11" s="3">
-        <v>46227</v>
-      </c>
-      <c r="D11" s="4">
-        <v>552871981</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46097</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="K11" s="3">
-        <v>46245</v>
-      </c>
-      <c r="L11" s="12">
-        <f ca="1">IF($O11="","",$O11-TODAY())</f>
-        <v>-113</v>
-      </c>
-      <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>292</v>
-      </c>
-      <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>292</v>
-      </c>
-      <c r="O11" s="6">
-        <v>46187</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="V11" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z11" s="7">
-        <v>5916.4</v>
-      </c>
-      <c r="AA11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="7">
-        <v>5916.4</v>
-      </c>
-      <c r="AE11" s="4">
-        <v>145</v>
-      </c>
-      <c r="AF11" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="AG11" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="AH11" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="AI11" s="5"/>
-      <c r="AJ11" s="4"/>
-      <c r="AK11" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="AL11" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM11" s="6">
-        <v>46217</v>
-      </c>
-      <c r="AN11" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN11" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <conditionalFormatting sqref="L2:L11">
+  <autoFilter ref="A1:AN9" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="expression" dxfId="79" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -8569,7 +8339,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M11">
+  <conditionalFormatting sqref="M2:M9">
     <cfRule type="expression" dxfId="74" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -8586,7 +8356,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N11">
+  <conditionalFormatting sqref="N2:N9">
     <cfRule type="expression" dxfId="69" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -8603,7 +8373,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U11">
+  <conditionalFormatting sqref="O2:U9">
     <cfRule type="expression" dxfId="64" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -8647,7 +8417,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A11" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A9" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
